--- a/data/matches/leagues/Finland_Veikkausliiga_2026.xlsx
+++ b/data/matches/leagues/Finland_Veikkausliiga_2026.xlsx
@@ -1596,7 +1596,7 @@
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>-1</v>
+        <v>3401</v>
       </c>
       <c r="BG2" t="n">
         <v>2</v>
@@ -2024,7 +2024,7 @@
         <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>-1</v>
+        <v>5041</v>
       </c>
       <c r="BG3" t="n">
         <v>2</v>
@@ -2452,7 +2452,7 @@
         <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>-1</v>
+        <v>1258</v>
       </c>
       <c r="BG4" t="n">
         <v>2</v>
@@ -2575,16 +2575,16 @@
         <v>1</v>
       </c>
       <c r="CU4" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="CV4" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="CW4" t="n">
         <v>1</v>
       </c>
       <c r="CX4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CY4" t="n">
         <v>3</v>
@@ -2777,22 +2777,22 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
         <v>7</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="V5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="W5" t="n">
         <v>6</v>
@@ -2801,10 +2801,10 @@
         <v>5</v>
       </c>
       <c r="Y5" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="Z5" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
@@ -2896,7 +2896,7 @@
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-1</v>
+        <v>4774</v>
       </c>
       <c r="BG5" t="n">
         <v>2</v>
@@ -2956,13 +2956,13 @@
         <v>106</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.42</v>
+        <v>1.74</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.01</v>
+        <v>3.27</v>
       </c>
       <c r="CC5" t="n">
         <v>0</v>
@@ -3019,10 +3019,10 @@
         <v>1</v>
       </c>
       <c r="CU5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="CV5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="CW5" t="n">
         <v>1</v>
@@ -3031,7 +3031,7 @@
         <v>6</v>
       </c>
       <c r="CY5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="CZ5" t="n">
         <v>0</v>
@@ -3193,10 +3193,10 @@
         <v>3</v>
       </c>
       <c r="M6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -3237,10 +3237,10 @@
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE6" t="n">
         <v>2.46</v>
@@ -3324,7 +3324,7 @@
         <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>-1</v>
+        <v>2470</v>
       </c>
       <c r="BG6" t="n">
         <v>2</v>
@@ -3357,16 +3357,16 @@
         <v>1</v>
       </c>
       <c r="BQ6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BR6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BS6" t="n">
         <v>2</v>
       </c>
       <c r="BT6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BU6" t="n">
         <v>1</v>
@@ -3631,13 +3631,13 @@
         <v>8</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T7" t="n">
         <v>7</v>
       </c>
       <c r="U7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="V7" t="n">
         <v>15</v>
@@ -3649,10 +3649,10 @@
         <v>6</v>
       </c>
       <c r="Y7" t="n">
+        <v>49</v>
+      </c>
+      <c r="Z7" t="n">
         <v>51</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>49</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-1</v>
+        <v>1853</v>
       </c>
       <c r="BG7" t="n">
         <v>2</v>
@@ -3812,13 +3812,13 @@
         <v>79</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="CA7" t="n">
         <v>1.77</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="CC7" t="n">
         <v>0</v>
@@ -3875,10 +3875,10 @@
         <v>1</v>
       </c>
       <c r="CU7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="CV7" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="CW7" t="n">
         <v>1</v>
@@ -3887,7 +3887,7 @@
         <v>8</v>
       </c>
       <c r="CY7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CZ7" t="n">
         <v>0</v>

--- a/data/matches/leagues/Finland_Veikkausliiga_2026.xlsx
+++ b/data/matches/leagues/Finland_Veikkausliiga_2026.xlsx
@@ -141,9 +141,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EH7" headerRowCount="1">
-  <autoFilter ref="A1:EH7"/>
-  <tableColumns count="138">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EJ13" headerRowCount="1">
+  <autoFilter ref="A1:EJ13"/>
+  <tableColumns count="140">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
     <tableColumn id="3" name="game_week"/>
@@ -270,18 +270,20 @@
     <tableColumn id="124" name="over45"/>
     <tableColumn id="125" name="over55"/>
     <tableColumn id="126" name="btts"/>
-    <tableColumn id="127" name="pinnacle_ft_2"/>
-    <tableColumn id="128" name="pinnacle_ft_x"/>
-    <tableColumn id="129" name="pinnacle_ft_1"/>
-    <tableColumn id="130" name="pinnacle_ft_over25"/>
-    <tableColumn id="131" name="pinnacle_ft_over15"/>
-    <tableColumn id="132" name="pinnacle_ft_over35"/>
-    <tableColumn id="133" name="pinnacle_1st_half_over15"/>
-    <tableColumn id="134" name="pinnacle_1st_half_under15"/>
-    <tableColumn id="135" name="pinnacle_corners_over_95"/>
-    <tableColumn id="136" name="pinnacle_corners_under_85"/>
-    <tableColumn id="137" name="pinnacle_corners_under_95"/>
-    <tableColumn id="138" name="pinnacle_corners_over_85"/>
+    <tableColumn id="127" name="pinnacle_ft_over35"/>
+    <tableColumn id="128" name="pinnacle_ft_over25"/>
+    <tableColumn id="129" name="pinnacle_ft_over15"/>
+    <tableColumn id="130" name="pinnacle_1st_half_over15"/>
+    <tableColumn id="131" name="pinnacle_1st_half_under15"/>
+    <tableColumn id="132" name="pinnacle_1st_half_over05"/>
+    <tableColumn id="133" name="pinnacle_1st_half_under05"/>
+    <tableColumn id="134" name="pinnacle_ft_2"/>
+    <tableColumn id="135" name="pinnacle_ft_x"/>
+    <tableColumn id="136" name="pinnacle_ft_1"/>
+    <tableColumn id="137" name="pinnacle_corners_over_95"/>
+    <tableColumn id="138" name="pinnacle_corners_under_95"/>
+    <tableColumn id="139" name="pinnacle_corners_over_85"/>
+    <tableColumn id="140" name="pinnacle_corners_under_85"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -576,7 +578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EH7"/>
+  <dimension ref="A1:EJ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.6" customWidth="1" min="1" max="1"/>
@@ -605,7 +607,7 @@
     <col width="16.8" customWidth="1" min="24" max="24"/>
     <col width="22.8" customWidth="1" min="25" max="25"/>
     <col width="22.8" customWidth="1" min="26" max="26"/>
-    <col width="22.8" customWidth="1" min="27" max="27"/>
+    <col width="26.4" customWidth="1" min="27" max="27"/>
     <col width="38.4" customWidth="1" min="28" max="28"/>
     <col width="21.6" customWidth="1" min="29" max="29"/>
     <col width="21.6" customWidth="1" min="30" max="30"/>
@@ -705,18 +707,20 @@
     <col width="9.6" customWidth="1" min="124" max="124"/>
     <col width="9.6" customWidth="1" min="125" max="125"/>
     <col width="8.4" customWidth="1" min="126" max="126"/>
-    <col width="18" customWidth="1" min="127" max="127"/>
-    <col width="18" customWidth="1" min="128" max="128"/>
-    <col width="18" customWidth="1" min="129" max="129"/>
-    <col width="24" customWidth="1" min="130" max="130"/>
-    <col width="24" customWidth="1" min="131" max="131"/>
-    <col width="24" customWidth="1" min="132" max="132"/>
-    <col width="31.2" customWidth="1" min="133" max="133"/>
-    <col width="32.4" customWidth="1" min="134" max="134"/>
-    <col width="31.2" customWidth="1" min="135" max="135"/>
-    <col width="32.4" customWidth="1" min="136" max="136"/>
-    <col width="32.4" customWidth="1" min="137" max="137"/>
-    <col width="31.2" customWidth="1" min="138" max="138"/>
+    <col width="24" customWidth="1" min="127" max="127"/>
+    <col width="24" customWidth="1" min="128" max="128"/>
+    <col width="24" customWidth="1" min="129" max="129"/>
+    <col width="31.2" customWidth="1" min="130" max="130"/>
+    <col width="32.4" customWidth="1" min="131" max="131"/>
+    <col width="31.2" customWidth="1" min="132" max="132"/>
+    <col width="32.4" customWidth="1" min="133" max="133"/>
+    <col width="18" customWidth="1" min="134" max="134"/>
+    <col width="18" customWidth="1" min="135" max="135"/>
+    <col width="18" customWidth="1" min="136" max="136"/>
+    <col width="31.2" customWidth="1" min="137" max="137"/>
+    <col width="32.4" customWidth="1" min="138" max="138"/>
+    <col width="31.2" customWidth="1" min="139" max="139"/>
+    <col width="32.4" customWidth="1" min="140" max="140"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1352,62 +1356,72 @@
       </c>
       <c r="DW1" s="1" t="inlineStr">
         <is>
+          <t>pinnacle_ft_over35</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_ft_over25</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_ft_over15</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_1st_half_over15</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_1st_half_under15</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_1st_half_over05</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_1st_half_under05</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
           <t>pinnacle_ft_2</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="EE1" s="1" t="inlineStr">
         <is>
           <t>pinnacle_ft_x</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="EF1" s="1" t="inlineStr">
         <is>
           <t>pinnacle_ft_1</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
-        <is>
-          <t>pinnacle_ft_over25</t>
-        </is>
-      </c>
-      <c r="EA1" s="1" t="inlineStr">
-        <is>
-          <t>pinnacle_ft_over15</t>
-        </is>
-      </c>
-      <c r="EB1" s="1" t="inlineStr">
-        <is>
-          <t>pinnacle_ft_over35</t>
-        </is>
-      </c>
-      <c r="EC1" s="1" t="inlineStr">
-        <is>
-          <t>pinnacle_1st_half_over15</t>
-        </is>
-      </c>
-      <c r="ED1" s="1" t="inlineStr">
-        <is>
-          <t>pinnacle_1st_half_under15</t>
-        </is>
-      </c>
-      <c r="EE1" s="1" t="inlineStr">
+      <c r="EG1" s="1" t="inlineStr">
         <is>
           <t>pinnacle_corners_over_95</t>
         </is>
       </c>
-      <c r="EF1" s="1" t="inlineStr">
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_corners_under_95</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_corners_over_85</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
         <is>
           <t>pinnacle_corners_under_85</t>
-        </is>
-      </c>
-      <c r="EG1" s="1" t="inlineStr">
-        <is>
-          <t>pinnacle_corners_under_95</t>
-        </is>
-      </c>
-      <c r="EH1" s="1" t="inlineStr">
-        <is>
-          <t>pinnacle_corners_over_85</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1760,7 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DE2" t="n">
         <v>1</v>
@@ -1779,7 +1793,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DP2" t="b">
         <v>0</v>
@@ -1804,48 +1818,50 @@
       </c>
       <c r="DW2" t="inlineStr">
         <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EB2" t="inlineStr"/>
+      <c r="EC2" t="inlineStr"/>
+      <c r="ED2" t="inlineStr">
+        <is>
           <t>7.56</t>
         </is>
       </c>
-      <c r="DX2" t="inlineStr">
+      <c r="EE2" t="inlineStr">
         <is>
           <t>4.90</t>
         </is>
       </c>
-      <c r="DY2" t="inlineStr">
+      <c r="EF2" t="inlineStr">
         <is>
           <t>1.41</t>
         </is>
       </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>1.20</t>
-        </is>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>2.46</t>
-        </is>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="EE2" t="inlineStr"/>
-      <c r="EF2" t="inlineStr"/>
       <c r="EG2" t="inlineStr"/>
       <c r="EH2" t="inlineStr"/>
+      <c r="EI2" t="inlineStr"/>
+      <c r="EJ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2174,7 +2190,7 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
@@ -2207,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2232,48 +2248,50 @@
       </c>
       <c r="DW3" t="inlineStr">
         <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="DX3" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="DY3" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="DZ3" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="EA3" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EB3" t="inlineStr"/>
+      <c r="EC3" t="inlineStr"/>
+      <c r="ED3" t="inlineStr">
+        <is>
           <t>5.15</t>
         </is>
       </c>
-      <c r="DX3" t="inlineStr">
+      <c r="EE3" t="inlineStr">
         <is>
           <t>4.51</t>
         </is>
       </c>
-      <c r="DY3" t="inlineStr">
+      <c r="EF3" t="inlineStr">
         <is>
           <t>1.59</t>
         </is>
       </c>
-      <c r="DZ3" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="EA3" t="inlineStr">
-        <is>
-          <t>1.15</t>
-        </is>
-      </c>
-      <c r="EB3" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="EC3" t="inlineStr">
-        <is>
-          <t>2.21</t>
-        </is>
-      </c>
-      <c r="ED3" t="inlineStr">
-        <is>
-          <t>1.69</t>
-        </is>
-      </c>
-      <c r="EE3" t="inlineStr"/>
-      <c r="EF3" t="inlineStr"/>
       <c r="EG3" t="inlineStr"/>
       <c r="EH3" t="inlineStr"/>
+      <c r="EI3" t="inlineStr"/>
+      <c r="EJ3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2635,7 +2653,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -2660,62 +2678,64 @@
       </c>
       <c r="DW4" t="inlineStr">
         <is>
+          <t>2.61</t>
+        </is>
+      </c>
+      <c r="DX4" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="DY4" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="DZ4" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="EA4" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EB4" t="inlineStr"/>
+      <c r="EC4" t="inlineStr"/>
+      <c r="ED4" t="inlineStr">
+        <is>
           <t>4.15</t>
         </is>
       </c>
-      <c r="DX4" t="inlineStr">
+      <c r="EE4" t="inlineStr">
         <is>
           <t>3.91</t>
         </is>
       </c>
-      <c r="DY4" t="inlineStr">
+      <c r="EF4" t="inlineStr">
         <is>
           <t>1.83</t>
         </is>
       </c>
-      <c r="DZ4" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="EA4" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="EB4" t="inlineStr">
-        <is>
-          <t>2.61</t>
-        </is>
-      </c>
-      <c r="EC4" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="ED4" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="EE4" t="inlineStr">
+      <c r="EG4" t="inlineStr">
         <is>
           <t>1.75</t>
         </is>
       </c>
-      <c r="EF4" t="inlineStr">
+      <c r="EH4" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EI4" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EJ4" t="inlineStr">
         <is>
           <t>2.59</t>
-        </is>
-      </c>
-      <c r="EG4" t="inlineStr">
-        <is>
-          <t>2.04</t>
-        </is>
-      </c>
-      <c r="EH4" t="inlineStr">
-        <is>
-          <t>1.45</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3099,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3104,48 +3124,50 @@
       </c>
       <c r="DW5" t="inlineStr">
         <is>
+          <t>2.59</t>
+        </is>
+      </c>
+      <c r="DX5" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="DY5" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="DZ5" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="EA5" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EB5" t="inlineStr"/>
+      <c r="EC5" t="inlineStr"/>
+      <c r="ED5" t="inlineStr">
+        <is>
           <t>3.71</t>
         </is>
       </c>
-      <c r="DX5" t="inlineStr">
+      <c r="EE5" t="inlineStr">
         <is>
           <t>3.37</t>
         </is>
       </c>
-      <c r="DY5" t="inlineStr">
+      <c r="EF5" t="inlineStr">
         <is>
           <t>2.11</t>
         </is>
       </c>
-      <c r="DZ5" t="inlineStr">
-        <is>
-          <t>1.68</t>
-        </is>
-      </c>
-      <c r="EA5" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
-      </c>
-      <c r="EB5" t="inlineStr">
-        <is>
-          <t>2.59</t>
-        </is>
-      </c>
-      <c r="EC5" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="ED5" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="EE5" t="inlineStr"/>
-      <c r="EF5" t="inlineStr"/>
       <c r="EG5" t="inlineStr"/>
       <c r="EH5" t="inlineStr"/>
+      <c r="EI5" t="inlineStr"/>
+      <c r="EJ5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3477,7 +3499,7 @@
         <v>0</v>
       </c>
       <c r="DE6" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -3507,7 +3529,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -3532,40 +3554,42 @@
       </c>
       <c r="DW6" t="inlineStr">
         <is>
+          <t>2.79</t>
+        </is>
+      </c>
+      <c r="DX6" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="DY6" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="DZ6" t="inlineStr"/>
+      <c r="EA6" t="inlineStr"/>
+      <c r="EB6" t="inlineStr"/>
+      <c r="EC6" t="inlineStr"/>
+      <c r="ED6" t="inlineStr">
+        <is>
           <t>2.47</t>
         </is>
       </c>
-      <c r="DX6" t="inlineStr">
+      <c r="EE6" t="inlineStr">
         <is>
           <t>3.57</t>
         </is>
       </c>
-      <c r="DY6" t="inlineStr">
+      <c r="EF6" t="inlineStr">
         <is>
           <t>2.83</t>
         </is>
       </c>
-      <c r="DZ6" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="EA6" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
-      </c>
-      <c r="EB6" t="inlineStr">
-        <is>
-          <t>2.79</t>
-        </is>
-      </c>
-      <c r="EC6" t="inlineStr"/>
-      <c r="ED6" t="inlineStr"/>
-      <c r="EE6" t="inlineStr"/>
-      <c r="EF6" t="inlineStr"/>
       <c r="EG6" t="inlineStr"/>
       <c r="EH6" t="inlineStr"/>
+      <c r="EI6" t="inlineStr"/>
+      <c r="EJ6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3935,7 +3959,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -3960,56 +3984,2742 @@
       </c>
       <c r="DW7" t="inlineStr">
         <is>
+          <t>2.67</t>
+        </is>
+      </c>
+      <c r="DX7" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="DY7" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="DZ7" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="EA7" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EB7" t="inlineStr"/>
+      <c r="EC7" t="inlineStr"/>
+      <c r="ED7" t="inlineStr">
+        <is>
           <t>2.38</t>
         </is>
       </c>
-      <c r="DX7" t="inlineStr">
+      <c r="EE7" t="inlineStr">
         <is>
           <t>3.59</t>
         </is>
       </c>
-      <c r="DY7" t="inlineStr">
+      <c r="EF7" t="inlineStr">
         <is>
           <t>2.94</t>
         </is>
       </c>
-      <c r="DZ7" t="inlineStr">
-        <is>
-          <t>1.69</t>
-        </is>
-      </c>
-      <c r="EA7" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="EB7" t="inlineStr">
+      <c r="EG7" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="EH7" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="EI7" t="inlineStr"/>
+      <c r="EJ7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Finland_Veikkausliiga_2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TPS</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Lahti</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>46122.625</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K8" t="n">
+        <v>6</v>
+      </c>
+      <c r="L8" t="n">
+        <v>11</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3</v>
+      </c>
+      <c r="N8" t="n">
+        <v>7</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>6</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6</v>
+      </c>
+      <c r="S8" t="n">
+        <v>8</v>
+      </c>
+      <c r="T8" t="n">
+        <v>12</v>
+      </c>
+      <c r="U8" t="n">
+        <v>14</v>
+      </c>
+      <c r="V8" t="n">
+        <v>18</v>
+      </c>
+      <c r="W8" t="n">
+        <v>16</v>
+      </c>
+      <c r="X8" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Veritas Stadion</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Hippoksentie 6, Åbo</t>
+        </is>
+      </c>
+      <c r="AC8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>415</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>9</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>49</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>50</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>85</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>78</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>3</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>3</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>50</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP8" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ8" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR8" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS8" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT8" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU8" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV8" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW8" t="inlineStr">
+        <is>
+          <t>3.07</t>
+        </is>
+      </c>
+      <c r="DX8" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="DY8" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="DZ8" t="inlineStr">
+        <is>
+          <t>2.81</t>
+        </is>
+      </c>
+      <c r="EA8" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EB8" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EC8" t="inlineStr">
+        <is>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="ED8" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="EE8" t="inlineStr">
+        <is>
+          <t>3.67</t>
+        </is>
+      </c>
+      <c r="EF8" t="inlineStr">
+        <is>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="EG8" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EH8" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EI8" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EJ8" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Finland_Veikkausliiga_2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SJK</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Mariehamn</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>46122.66666666666</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>6</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" t="n">
+        <v>8</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>6</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>11</v>
+      </c>
+      <c r="V9" t="n">
+        <v>3</v>
+      </c>
+      <c r="W9" t="n">
+        <v>14</v>
+      </c>
+      <c r="X9" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>51</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>49</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>OmaSP Stadion</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Alaseinäjoenkatu 9, Seinäjoki</t>
+        </is>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>102</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>75</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>23</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>106</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>90</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>12</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>3</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP9" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ9" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR9" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS9" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT9" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU9" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV9" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW9" t="inlineStr">
+        <is>
+          <t>2.81</t>
+        </is>
+      </c>
+      <c r="DX9" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="DY9" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="DZ9" t="inlineStr">
+        <is>
+          <t>2.61</t>
+        </is>
+      </c>
+      <c r="EA9" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EB9" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EC9" t="inlineStr">
+        <is>
+          <t>3.37</t>
+        </is>
+      </c>
+      <c r="ED9" t="inlineStr">
+        <is>
+          <t>5.59</t>
+        </is>
+      </c>
+      <c r="EE9" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="EF9" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EG9" t="inlineStr"/>
+      <c r="EH9" t="inlineStr"/>
+      <c r="EI9" t="inlineStr"/>
+      <c r="EJ9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Finland_Veikkausliiga_2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VPS</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Jaro</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>46122.70833333334</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6</v>
+      </c>
+      <c r="L10" t="n">
+        <v>10</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>5</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>13</v>
+      </c>
+      <c r="U10" t="n">
+        <v>7</v>
+      </c>
+      <c r="V10" t="n">
+        <v>18</v>
+      </c>
+      <c r="W10" t="n">
+        <v>11</v>
+      </c>
+      <c r="X10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>54</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>60</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>68</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>124</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>129</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP10" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ10" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR10" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS10" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT10" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU10" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV10" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW10" t="inlineStr">
+        <is>
+          <t>3.27</t>
+        </is>
+      </c>
+      <c r="DX10" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="DY10" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="DZ10" t="inlineStr">
+        <is>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="EA10" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EB10" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EC10" t="inlineStr">
+        <is>
+          <t>3.08</t>
+        </is>
+      </c>
+      <c r="ED10" t="inlineStr">
+        <is>
+          <t>3.71</t>
+        </is>
+      </c>
+      <c r="EE10" t="inlineStr">
+        <is>
+          <t>3.67</t>
+        </is>
+      </c>
+      <c r="EF10" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EG10" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EH10" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EI10" t="inlineStr"/>
+      <c r="EJ10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Finland_Veikkausliiga_2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>KuPS</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Gnistan</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>46123.45833333334</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>9</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>12</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>11</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S11" t="n">
+        <v>8</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>19</v>
+      </c>
+      <c r="V11" t="n">
+        <v>7</v>
+      </c>
+      <c r="W11" t="n">
+        <v>8</v>
+      </c>
+      <c r="X11" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>75</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Savon Sanomat Areena</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Kaartokatu 6, Kuopio</t>
+        </is>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>411</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>96</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>25</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>153</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>59</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>28</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>13</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>3</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>3</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP11" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ11" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR11" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS11" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT11" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU11" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV11" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW11" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="DX11" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="DY11" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="DZ11" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EA11" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EB11" t="inlineStr"/>
+      <c r="EC11" t="inlineStr"/>
+      <c r="ED11" t="inlineStr">
+        <is>
+          <t>7.24</t>
+        </is>
+      </c>
+      <c r="EE11" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="EF11" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EG11" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EH11" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EI11" t="inlineStr"/>
+      <c r="EJ11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Finland_Veikkausliiga_2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>HJK</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Oulu</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>46123.58333333334</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L12" t="n">
+        <v>7</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3</v>
+      </c>
+      <c r="R12" t="n">
+        <v>3</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>6</v>
+      </c>
+      <c r="V12" t="n">
+        <v>7</v>
+      </c>
+      <c r="W12" t="n">
+        <v>7</v>
+      </c>
+      <c r="X12" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>425</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>68</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>44</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>123</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>78</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>26</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>29</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>7</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>100</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>100</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>3</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>3</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>3</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP12" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ12" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR12" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS12" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT12" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU12" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV12" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW12" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="DX12" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="DY12" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="DZ12" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EA12" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EB12" t="inlineStr"/>
+      <c r="EC12" t="inlineStr"/>
+      <c r="ED12" t="inlineStr">
+        <is>
+          <t>4.64</t>
+        </is>
+      </c>
+      <c r="EE12" t="inlineStr">
+        <is>
+          <t>4.41</t>
+        </is>
+      </c>
+      <c r="EF12" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EG12" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EH12" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EI12" t="inlineStr"/>
+      <c r="EJ12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Finland_Veikkausliiga_2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Inter Turku</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Ilves</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>46123.66666666666</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>9</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4</v>
+      </c>
+      <c r="L13" t="n">
+        <v>13</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>6</v>
+      </c>
+      <c r="V13" t="n">
+        <v>4</v>
+      </c>
+      <c r="W13" t="n">
+        <v>10</v>
+      </c>
+      <c r="X13" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Veritas Stadion</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>Hippoksentie 6, Åbo</t>
+        </is>
+      </c>
+      <c r="AC13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>406</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>8</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>11</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>73</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>23</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>118</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>84</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>24</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>2</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>50</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP13" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ13" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR13" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS13" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT13" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU13" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV13" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW13" t="inlineStr">
+        <is>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="DX13" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="DY13" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="DZ13" t="inlineStr">
         <is>
           <t>2.67</t>
         </is>
       </c>
-      <c r="EC7" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="ED7" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="EE7" t="inlineStr">
-        <is>
-          <t>1.59</t>
-        </is>
-      </c>
-      <c r="EF7" t="inlineStr"/>
-      <c r="EG7" t="inlineStr">
-        <is>
-          <t>2.26</t>
-        </is>
-      </c>
-      <c r="EH7" t="inlineStr"/>
+      <c r="EA13" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EB13" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EC13" t="inlineStr">
+        <is>
+          <t>3.38</t>
+        </is>
+      </c>
+      <c r="ED13" t="inlineStr">
+        <is>
+          <t>3.38</t>
+        </is>
+      </c>
+      <c r="EE13" t="inlineStr">
+        <is>
+          <t>3.44</t>
+        </is>
+      </c>
+      <c r="EF13" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="EG13" t="inlineStr"/>
+      <c r="EH13" t="inlineStr"/>
+      <c r="EI13" t="inlineStr"/>
+      <c r="EJ13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Finland_Veikkausliiga_2026.xlsx
+++ b/data/matches/leagues/Finland_Veikkausliiga_2026.xlsx
@@ -129,8 +129,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EJ47" headerRowCount="1">
-  <autoFilter ref="A1:EJ47"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EJ53" headerRowCount="1">
+  <autoFilter ref="A1:EJ53"/>
   <tableColumns count="140">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EJ47"/>
+  <dimension ref="A1:EJ53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.6" customWidth="1" min="1" max="1"/>
@@ -1748,7 +1748,7 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="DE2" t="n">
         <v>1.25</v>
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP2" t="b">
         <v>0</v>
@@ -2211,7 +2211,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2297,12 +2297,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>TPS</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F4" s="1" t="n">
@@ -2312,25 +2312,25 @@
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -2339,28 +2339,28 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S4" t="n">
+        <v>9</v>
+      </c>
+      <c r="T4" t="n">
+        <v>5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>14</v>
+      </c>
+      <c r="V4" t="n">
+        <v>12</v>
+      </c>
+      <c r="W4" t="n">
         <v>6</v>
       </c>
-      <c r="T4" t="n">
-        <v>13</v>
-      </c>
-      <c r="U4" t="n">
-        <v>7</v>
-      </c>
-      <c r="V4" t="n">
-        <v>17</v>
-      </c>
-      <c r="W4" t="n">
-        <v>13</v>
-      </c>
       <c r="X4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Y4" t="n">
         <v>49</v>
@@ -2371,278 +2371,278 @@
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="AF4" t="n">
-        <v>3.6</v>
+        <v>2.95</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.52</v>
+        <v>1.76</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.28</v>
+        <v>2.51</v>
       </c>
       <c r="AK4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>411</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>4774</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>70</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>38</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>112</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>106</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="CA4" t="n">
         <v>1.53</v>
       </c>
-      <c r="AL4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>1258</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ4" t="n">
+      <c r="CB4" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>1</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW4" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY4" t="n">
+        <v>11</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO4" t="n">
         <v>9</v>
       </c>
-      <c r="BK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>9</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>36</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>68</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>75</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>96</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="CB4" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="CC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI4" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ4" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ4" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR4" t="n">
-        <v>22</v>
-      </c>
-      <c r="CS4" t="n">
-        <v>23</v>
-      </c>
-      <c r="CT4" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU4" t="n">
-        <v>2</v>
-      </c>
-      <c r="CV4" t="n">
-        <v>3</v>
-      </c>
-      <c r="CW4" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX4" t="n">
-        <v>9</v>
-      </c>
-      <c r="CY4" t="n">
-        <v>3</v>
-      </c>
-      <c r="CZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="DE4" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="DF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DO4" t="n">
-        <v>7</v>
-      </c>
       <c r="DP4" t="b">
         <v>1</v>
       </c>
@@ -2650,10 +2650,10 @@
         <v>1</v>
       </c>
       <c r="DR4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT4" t="b">
         <v>0</v>
@@ -2664,19 +2664,11 @@
       <c r="DV4" t="b">
         <v>1</v>
       </c>
-      <c r="DW4" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="DX4" t="inlineStr">
-        <is>
-          <t>2.04</t>
-        </is>
-      </c>
+      <c r="DW4" t="inlineStr"/>
+      <c r="DX4" t="inlineStr"/>
       <c r="DY4" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="DZ4" t="inlineStr">
@@ -2688,44 +2680,36 @@
       <c r="EB4" t="inlineStr"/>
       <c r="EC4" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="ED4" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="EE4" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="EF4" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EG4" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="EH4" t="inlineStr">
         <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="EI4" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="EJ4" t="inlineStr">
-        <is>
-          <t>2.59</t>
-        </is>
-      </c>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="EI4" t="inlineStr"/>
+      <c r="EJ4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2743,12 +2727,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="F5" s="1" t="n">
@@ -2758,55 +2742,55 @@
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>10</v>
+      </c>
+      <c r="L5" t="n">
+        <v>10</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
         <v>4</v>
       </c>
-      <c r="J5" t="n">
-        <v>4</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L5" t="n">
+      <c r="S5" t="n">
+        <v>6</v>
+      </c>
+      <c r="T5" t="n">
+        <v>13</v>
+      </c>
+      <c r="U5" t="n">
         <v>7</v>
       </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>5</v>
-      </c>
-      <c r="R5" t="n">
-        <v>7</v>
-      </c>
-      <c r="S5" t="n">
-        <v>9</v>
-      </c>
-      <c r="T5" t="n">
-        <v>5</v>
-      </c>
-      <c r="U5" t="n">
-        <v>14</v>
-      </c>
       <c r="V5" t="n">
+        <v>17</v>
+      </c>
+      <c r="W5" t="n">
+        <v>13</v>
+      </c>
+      <c r="X5" t="n">
         <v>12</v>
-      </c>
-      <c r="W5" t="n">
-        <v>6</v>
-      </c>
-      <c r="X5" t="n">
-        <v>5</v>
       </c>
       <c r="Y5" t="n">
         <v>49</v>
@@ -2817,230 +2801,230 @@
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.95</v>
+        <v>3.6</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.76</v>
+        <v>1.52</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.51</v>
+        <v>2.28</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL5" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.97</v>
+        <v>1.52</v>
       </c>
       <c r="AO5" t="n">
-        <v>2.53</v>
+        <v>3.1</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AS5" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>1258</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>9</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>68</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>75</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>96</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>2</v>
+      </c>
+      <c r="CV5" t="n">
         <v>3</v>
       </c>
-      <c r="AT5" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>411</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>4774</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>2</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM5" t="n">
+      <c r="CW5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY5" t="n">
         <v>3</v>
       </c>
-      <c r="BN5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>70</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>38</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>112</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>106</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="CB5" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="CC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI5" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ5" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ5" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>21</v>
-      </c>
-      <c r="CS5" t="n">
-        <v>16</v>
-      </c>
-      <c r="CT5" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU5" t="n">
-        <v>1</v>
-      </c>
-      <c r="CV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CW5" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX5" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY5" t="n">
-        <v>11</v>
-      </c>
       <c r="CZ5" t="n">
         <v>0</v>
       </c>
@@ -3054,10 +3038,10 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="DE5" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3096,10 +3080,10 @@
         <v>1</v>
       </c>
       <c r="DR5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT5" t="b">
         <v>0</v>
@@ -3110,11 +3094,19 @@
       <c r="DV5" t="b">
         <v>1</v>
       </c>
-      <c r="DW5" t="inlineStr"/>
-      <c r="DX5" t="inlineStr"/>
+      <c r="DW5" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="DX5" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
       <c r="DY5" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="DZ5" t="inlineStr">
@@ -3126,36 +3118,44 @@
       <c r="EB5" t="inlineStr"/>
       <c r="EC5" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="ED5" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="EE5" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="EF5" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="EG5" t="inlineStr">
         <is>
+          <t>2.61</t>
+        </is>
+      </c>
+      <c r="EH5" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="EI5" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EJ5" t="inlineStr">
+        <is>
           <t>2.59</t>
         </is>
       </c>
-      <c r="EH5" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
-      </c>
-      <c r="EI5" t="inlineStr"/>
-      <c r="EJ5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3484,10 +3484,10 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.67</v>
+        <v>1.25</v>
       </c>
       <c r="DE6" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -3517,7 +3517,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -3917,7 +3917,7 @@
         <v>1.5</v>
       </c>
       <c r="DE7" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -3947,7 +3947,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4363,7 +4363,7 @@
         <v>2.5</v>
       </c>
       <c r="DE8" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4393,7 +4393,7 @@
         <v>0.77</v>
       </c>
       <c r="DO8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -4822,10 +4822,10 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -4855,7 +4855,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5260,7 +5260,7 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="DE10" t="n">
         <v>0.4</v>
@@ -5293,7 +5293,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP10" t="b">
         <v>0</v>
@@ -5714,10 +5714,10 @@
         <v>0</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="DF11" t="n">
         <v>0</v>
@@ -5747,7 +5747,7 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6155,7 +6155,7 @@
         <v>1.75</v>
       </c>
       <c r="DE12" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="DF12" t="n">
         <v>3</v>
@@ -6185,7 +6185,7 @@
         <v>3.72</v>
       </c>
       <c r="DO12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -6598,7 +6598,7 @@
         <v>0</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="DE13" t="n">
         <v>0.6</v>
@@ -6631,7 +6631,7 @@
         <v>1.7</v>
       </c>
       <c r="DO13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7047,7 +7047,7 @@
         <v>1.5</v>
       </c>
       <c r="DE14" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="DF14" t="n">
         <v>0</v>
@@ -7077,7 +7077,7 @@
         <v>1.46</v>
       </c>
       <c r="DO14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -7482,7 +7482,7 @@
         <v>100</v>
       </c>
       <c r="DD15" t="n">
-        <v>0.67</v>
+        <v>1.25</v>
       </c>
       <c r="DE15" t="n">
         <v>1.25</v>
@@ -7515,7 +7515,7 @@
         <v>2.82</v>
       </c>
       <c r="DO15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -7953,7 +7953,7 @@
         <v>0.29</v>
       </c>
       <c r="DO16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8407,7 +8407,7 @@
         <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -8869,7 +8869,7 @@
         <v>2.53</v>
       </c>
       <c r="DO18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9299,7 +9299,7 @@
         <v>1.42</v>
       </c>
       <c r="DO19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -9704,10 +9704,10 @@
         <v>50</v>
       </c>
       <c r="DD20" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="DE20" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="DF20" t="n">
         <v>3</v>
@@ -9737,7 +9737,7 @@
         <v>4.58</v>
       </c>
       <c r="DO20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10142,7 +10142,7 @@
         <v>50</v>
       </c>
       <c r="DD21" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="DE21" t="n">
         <v>0.6</v>
@@ -10175,7 +10175,7 @@
         <v>2.08</v>
       </c>
       <c r="DO21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -10591,7 +10591,7 @@
         <v>2.5</v>
       </c>
       <c r="DE22" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="DF22" t="n">
         <v>3</v>
@@ -10621,7 +10621,7 @@
         <v>2.57</v>
       </c>
       <c r="DO22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11034,7 +11034,7 @@
         <v>50</v>
       </c>
       <c r="DD23" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="DE23" t="n">
         <v>0.4</v>
@@ -11067,7 +11067,7 @@
         <v>4.2</v>
       </c>
       <c r="DO23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -11483,7 +11483,7 @@
         <v>1.25</v>
       </c>
       <c r="DE24" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="DF24" t="n">
         <v>0</v>
@@ -11513,7 +11513,7 @@
         <v>2.86</v>
       </c>
       <c r="DO24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -11926,10 +11926,10 @@
         <v>75</v>
       </c>
       <c r="DD25" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="DE25" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DF25" t="n">
         <v>2</v>
@@ -11959,7 +11959,7 @@
         <v>2.01</v>
       </c>
       <c r="DO25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -12372,10 +12372,10 @@
         <v>75</v>
       </c>
       <c r="DD26" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="DE26" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="DF26" t="n">
         <v>3</v>
@@ -12405,7 +12405,7 @@
         <v>3.65</v>
       </c>
       <c r="DO26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -12802,10 +12802,10 @@
         <v>67</v>
       </c>
       <c r="DD27" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="DE27" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="DF27" t="n">
         <v>2.33</v>
@@ -12835,7 +12835,7 @@
         <v>3.04</v>
       </c>
       <c r="DO27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -13248,7 +13248,7 @@
         <v>100</v>
       </c>
       <c r="DD28" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="DE28" t="n">
         <v>0.6</v>
@@ -13281,7 +13281,7 @@
         <v>2.9</v>
       </c>
       <c r="DO28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -13367,363 +13367,363 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>TPS</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F29" s="1" t="n">
         <v>46144.58333333334</v>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="n">
         <v>4</v>
       </c>
-      <c r="J29" t="n">
-        <v>6</v>
-      </c>
       <c r="K29" t="n">
+        <v>8</v>
+      </c>
+      <c r="L29" t="n">
+        <v>12</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2</v>
+      </c>
+      <c r="R29" t="n">
+        <v>10</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3</v>
+      </c>
+      <c r="T29" t="n">
+        <v>10</v>
+      </c>
+      <c r="U29" t="n">
         <v>5</v>
       </c>
-      <c r="L29" t="n">
-        <v>11</v>
-      </c>
-      <c r="M29" t="n">
-        <v>2</v>
-      </c>
-      <c r="N29" t="n">
-        <v>4</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>4</v>
-      </c>
-      <c r="R29" t="n">
-        <v>6</v>
-      </c>
-      <c r="S29" t="n">
-        <v>6</v>
-      </c>
-      <c r="T29" t="n">
-        <v>4</v>
-      </c>
-      <c r="U29" t="n">
-        <v>10</v>
-      </c>
       <c r="V29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="W29" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="X29" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Y29" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="Z29" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="AA29" t="inlineStr"/>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.2</v>
+        <v>2.76</v>
       </c>
       <c r="AF29" t="n">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="AG29" t="n">
-        <v>3.22</v>
+        <v>2.1</v>
       </c>
       <c r="AH29" t="n">
         <v>1.28</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AJ29" t="n">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AL29" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AM29" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT29" t="n">
         <v>1.41</v>
       </c>
-      <c r="AN29" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AU29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>408</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>1003</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BI29" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ29" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>6</v>
+      </c>
+      <c r="BM29" t="n">
         <v>4</v>
       </c>
-      <c r="AV29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB29" t="n">
+      <c r="BN29" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV29" t="n">
+        <v>40</v>
+      </c>
+      <c r="BW29" t="n">
+        <v>64</v>
+      </c>
+      <c r="BX29" t="n">
+        <v>90</v>
+      </c>
+      <c r="BY29" t="n">
+        <v>88</v>
+      </c>
+      <c r="BZ29" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="CA29" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="CB29" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="CC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI29" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ29" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM29" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO29" t="n">
         <v>-1</v>
       </c>
-      <c r="BC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD29" t="n">
+      <c r="CP29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CQ29" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR29" t="n">
+        <v>34</v>
+      </c>
+      <c r="CS29" t="n">
+        <v>30</v>
+      </c>
+      <c r="CT29" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU29" t="n">
+        <v>3</v>
+      </c>
+      <c r="CV29" t="n">
+        <v>1</v>
+      </c>
+      <c r="CW29" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX29" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY29" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ29" t="n">
+        <v>25</v>
+      </c>
+      <c r="DA29" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB29" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC29" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD29" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DE29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DF29" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DH29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DI29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DJ29" t="n">
         <v>75</v>
       </c>
-      <c r="BE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>1864</v>
-      </c>
-      <c r="BG29" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH29" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ29" t="n">
-        <v>3</v>
-      </c>
-      <c r="BK29" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL29" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM29" t="n">
-        <v>3</v>
-      </c>
-      <c r="BN29" t="n">
+      <c r="DK29" t="n">
+        <v>50</v>
+      </c>
+      <c r="DL29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DM29" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="DN29" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="DO29" t="n">
         <v>8</v>
       </c>
-      <c r="BO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP29" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ29" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR29" t="n">
-        <v>3</v>
-      </c>
-      <c r="BS29" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT29" t="n">
-        <v>5</v>
-      </c>
-      <c r="BU29" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV29" t="n">
-        <v>73</v>
-      </c>
-      <c r="BW29" t="n">
-        <v>59</v>
-      </c>
-      <c r="BX29" t="n">
-        <v>111</v>
-      </c>
-      <c r="BY29" t="n">
-        <v>91</v>
-      </c>
-      <c r="BZ29" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="CA29" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="CB29" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="CC29" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE29" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI29" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ29" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ29" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR29" t="n">
-        <v>18</v>
-      </c>
-      <c r="CS29" t="n">
-        <v>22</v>
-      </c>
-      <c r="CT29" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU29" t="n">
-        <v>2</v>
-      </c>
-      <c r="CV29" t="n">
-        <v>4</v>
-      </c>
-      <c r="CW29" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX29" t="n">
-        <v>8</v>
-      </c>
-      <c r="CY29" t="n">
-        <v>3</v>
-      </c>
-      <c r="CZ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA29" t="n">
-        <v>75</v>
-      </c>
-      <c r="DB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC29" t="n">
-        <v>100</v>
-      </c>
-      <c r="DD29" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="DE29" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="DF29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DG29" t="n">
-        <v>1</v>
-      </c>
-      <c r="DH29" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="DI29" t="n">
-        <v>2</v>
-      </c>
-      <c r="DJ29" t="n">
-        <v>100</v>
-      </c>
-      <c r="DK29" t="n">
-        <v>25</v>
-      </c>
-      <c r="DL29" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="DM29" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="DN29" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="DO29" t="n">
-        <v>7</v>
-      </c>
       <c r="DP29" t="b">
         <v>1</v>
       </c>
       <c r="DQ29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT29" t="b">
         <v>0</v>
@@ -13732,58 +13732,58 @@
         <v>0</v>
       </c>
       <c r="DV29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW29" t="inlineStr"/>
       <c r="DX29" t="inlineStr"/>
       <c r="DY29" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="DZ29" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="EA29" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="EB29" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="EC29" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="ED29" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="EE29" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="EF29" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EG29" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="EH29" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="EI29" t="inlineStr"/>
@@ -13805,363 +13805,363 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="F30" s="1" t="n">
         <v>46144.58333333334</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J30" t="n">
+        <v>6</v>
+      </c>
+      <c r="K30" t="n">
+        <v>5</v>
+      </c>
+      <c r="L30" t="n">
+        <v>11</v>
+      </c>
+      <c r="M30" t="n">
+        <v>2</v>
+      </c>
+      <c r="N30" t="n">
         <v>4</v>
       </c>
-      <c r="K30" t="n">
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>4</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6</v>
+      </c>
+      <c r="S30" t="n">
+        <v>6</v>
+      </c>
+      <c r="T30" t="n">
+        <v>4</v>
+      </c>
+      <c r="U30" t="n">
+        <v>10</v>
+      </c>
+      <c r="V30" t="n">
+        <v>10</v>
+      </c>
+      <c r="W30" t="n">
+        <v>19</v>
+      </c>
+      <c r="X30" t="n">
         <v>8</v>
       </c>
-      <c r="L30" t="n">
-        <v>12</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>2</v>
-      </c>
-      <c r="R30" t="n">
-        <v>10</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3</v>
-      </c>
-      <c r="T30" t="n">
-        <v>10</v>
-      </c>
-      <c r="U30" t="n">
-        <v>5</v>
-      </c>
-      <c r="V30" t="n">
-        <v>20</v>
-      </c>
-      <c r="W30" t="n">
-        <v>12</v>
-      </c>
-      <c r="X30" t="n">
-        <v>12</v>
-      </c>
       <c r="Y30" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="Z30" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="AA30" t="inlineStr"/>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.76</v>
+        <v>2.2</v>
       </c>
       <c r="AF30" t="n">
-        <v>3.35</v>
+        <v>3.42</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.1</v>
+        <v>3.22</v>
       </c>
       <c r="AH30" t="n">
         <v>1.28</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AJ30" t="n">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.79</v>
+        <v>1.98</v>
       </c>
       <c r="AO30" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AP30" t="n">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="AQ30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AT30" t="n">
         <v>1.37</v>
       </c>
-      <c r="AR30" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AU30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW30" t="n">
         <v>1</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB30" t="n">
-        <v>408</v>
+        <v>-1</v>
       </c>
       <c r="BC30" t="n">
         <v>0</v>
       </c>
       <c r="BD30" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="BE30" t="n">
         <v>0</v>
       </c>
       <c r="BF30" t="n">
-        <v>1003</v>
+        <v>1864</v>
       </c>
       <c r="BG30" t="n">
         <v>2</v>
       </c>
       <c r="BH30" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BI30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BJ30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BK30" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM30" t="n">
         <v>3</v>
       </c>
-      <c r="BL30" t="n">
-        <v>6</v>
-      </c>
-      <c r="BM30" t="n">
+      <c r="BN30" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ30" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR30" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT30" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV30" t="n">
+        <v>73</v>
+      </c>
+      <c r="BW30" t="n">
+        <v>59</v>
+      </c>
+      <c r="BX30" t="n">
+        <v>111</v>
+      </c>
+      <c r="BY30" t="n">
+        <v>91</v>
+      </c>
+      <c r="BZ30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="CA30" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="CB30" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="CC30" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE30" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI30" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ30" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ30" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR30" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS30" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT30" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU30" t="n">
+        <v>2</v>
+      </c>
+      <c r="CV30" t="n">
         <v>4</v>
       </c>
-      <c r="BN30" t="n">
-        <v>9</v>
-      </c>
-      <c r="BO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU30" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV30" t="n">
-        <v>40</v>
-      </c>
-      <c r="BW30" t="n">
-        <v>64</v>
-      </c>
-      <c r="BX30" t="n">
-        <v>90</v>
-      </c>
-      <c r="BY30" t="n">
-        <v>88</v>
-      </c>
-      <c r="BZ30" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="CA30" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="CB30" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="CC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI30" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ30" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK30" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL30" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM30" t="n">
-        <v>2</v>
-      </c>
-      <c r="CN30" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO30" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CP30" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CQ30" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR30" t="n">
-        <v>34</v>
-      </c>
-      <c r="CS30" t="n">
-        <v>30</v>
-      </c>
-      <c r="CT30" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU30" t="n">
+      <c r="CW30" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX30" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY30" t="n">
         <v>3</v>
       </c>
-      <c r="CV30" t="n">
-        <v>1</v>
-      </c>
-      <c r="CW30" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX30" t="n">
-        <v>11</v>
-      </c>
-      <c r="CY30" t="n">
-        <v>5</v>
-      </c>
       <c r="CZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA30" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC30" t="n">
+        <v>100</v>
+      </c>
+      <c r="DD30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DE30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DF30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DG30" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH30" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DI30" t="n">
+        <v>2</v>
+      </c>
+      <c r="DJ30" t="n">
+        <v>100</v>
+      </c>
+      <c r="DK30" t="n">
         <v>25</v>
       </c>
-      <c r="DA30" t="n">
-        <v>50</v>
-      </c>
-      <c r="DB30" t="n">
-        <v>25</v>
-      </c>
-      <c r="DC30" t="n">
-        <v>50</v>
-      </c>
-      <c r="DD30" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="DE30" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="DF30" t="n">
-        <v>1</v>
-      </c>
-      <c r="DG30" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DH30" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DI30" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="DJ30" t="n">
-        <v>75</v>
-      </c>
-      <c r="DK30" t="n">
-        <v>50</v>
-      </c>
       <c r="DL30" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="DM30" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.84</v>
       </c>
       <c r="DN30" t="n">
-        <v>2.02</v>
+        <v>3.03</v>
       </c>
       <c r="DO30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
       </c>
       <c r="DQ30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT30" t="b">
         <v>0</v>
@@ -14170,58 +14170,58 @@
         <v>0</v>
       </c>
       <c r="DV30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW30" t="inlineStr"/>
       <c r="DX30" t="inlineStr"/>
       <c r="DY30" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="DZ30" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="EA30" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="EB30" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="EC30" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="ED30" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="EE30" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="EF30" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EG30" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="EH30" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="EI30" t="inlineStr"/>
@@ -14595,7 +14595,7 @@
         <v>2.61</v>
       </c>
       <c r="DO31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -15019,7 +15019,7 @@
         <v>1.75</v>
       </c>
       <c r="DE32" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="DF32" t="n">
         <v>1.5</v>
@@ -15049,7 +15049,7 @@
         <v>2.98</v>
       </c>
       <c r="DO32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -15495,7 +15495,7 @@
         <v>2.64</v>
       </c>
       <c r="DO33" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -15569,12 +15569,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>TPS</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="F34" s="1" t="n">
@@ -15590,13 +15590,13 @@
         <v>1</v>
       </c>
       <c r="J34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K34" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="L34" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="M34" t="n">
         <v>2</v>
@@ -15611,45 +15611,37 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T34" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="U34" t="n">
         <v>5</v>
       </c>
       <c r="V34" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="W34" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="X34" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="Y34" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Z34" t="n">
-        <v>67</v>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>Veritas Stadion</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>Hippoksentie 6, Åbo</t>
-        </is>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="n">
         <v>2</v>
       </c>
@@ -15657,88 +15649,88 @@
         <v>1</v>
       </c>
       <c r="AE34" t="n">
-        <v>4.6</v>
+        <v>2.56</v>
       </c>
       <c r="AF34" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.6</v>
+        <v>2.44</v>
       </c>
       <c r="AH34" t="n">
         <v>1.19</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AJ34" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR34" t="n">
         <v>2.45</v>
       </c>
-      <c r="AK34" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AS34" t="n">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AU34" t="n">
         <v>1</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW34" t="n">
         <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
         <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB34" t="n">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="BC34" t="n">
         <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="BE34" t="n">
         <v>0</v>
       </c>
       <c r="BF34" t="n">
-        <v>3547</v>
+        <v>4308</v>
       </c>
       <c r="BG34" t="n">
         <v>2</v>
@@ -15747,23 +15739,23 @@
         <v>1</v>
       </c>
       <c r="BI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ34" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK34" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL34" t="n">
         <v>3</v>
       </c>
-      <c r="BJ34" t="n">
+      <c r="BM34" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN34" t="n">
         <v>5</v>
       </c>
-      <c r="BK34" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL34" t="n">
-        <v>6</v>
-      </c>
-      <c r="BM34" t="n">
-        <v>8</v>
-      </c>
-      <c r="BN34" t="n">
-        <v>7</v>
-      </c>
       <c r="BO34" t="n">
         <v>1</v>
       </c>
@@ -15786,25 +15778,25 @@
         <v>1</v>
       </c>
       <c r="BV34" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="BW34" t="n">
-        <v>89</v>
+        <v>54</v>
       </c>
       <c r="BX34" t="n">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="BY34" t="n">
         <v>131</v>
       </c>
       <c r="BZ34" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="CA34" t="n">
-        <v>2.31</v>
+        <v>1.17</v>
       </c>
       <c r="CB34" t="n">
-        <v>3.11</v>
+        <v>1.92</v>
       </c>
       <c r="CC34" t="n">
         <v>0</v>
@@ -15840,10 +15832,10 @@
         <v>0</v>
       </c>
       <c r="CN34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP34" t="n">
         <v>0</v>
@@ -15852,77 +15844,77 @@
         <v>1</v>
       </c>
       <c r="CR34" t="n">
+        <v>15</v>
+      </c>
+      <c r="CS34" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT34" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU34" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV34" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW34" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX34" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY34" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ34" t="n">
+        <v>88</v>
+      </c>
+      <c r="DA34" t="n">
+        <v>88</v>
+      </c>
+      <c r="DB34" t="n">
+        <v>88</v>
+      </c>
+      <c r="DC34" t="n">
+        <v>100</v>
+      </c>
+      <c r="DD34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DH34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DI34" t="n">
+        <v>2</v>
+      </c>
+      <c r="DJ34" t="n">
+        <v>13</v>
+      </c>
+      <c r="DK34" t="n">
+        <v>13</v>
+      </c>
+      <c r="DL34" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="DM34" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DN34" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="DO34" t="n">
         <v>9</v>
       </c>
-      <c r="CS34" t="n">
-        <v>37</v>
-      </c>
-      <c r="CT34" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU34" t="n">
-        <v>11</v>
-      </c>
-      <c r="CV34" t="n">
-        <v>13</v>
-      </c>
-      <c r="CW34" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX34" t="n">
-        <v>19</v>
-      </c>
-      <c r="CY34" t="n">
-        <v>3</v>
-      </c>
-      <c r="CZ34" t="n">
-        <v>33</v>
-      </c>
-      <c r="DA34" t="n">
-        <v>100</v>
-      </c>
-      <c r="DB34" t="n">
-        <v>17</v>
-      </c>
-      <c r="DC34" t="n">
-        <v>84</v>
-      </c>
-      <c r="DD34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="DE34" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="DF34" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="DG34" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="DH34" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="DI34" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="DJ34" t="n">
-        <v>67</v>
-      </c>
-      <c r="DK34" t="n">
-        <v>0</v>
-      </c>
-      <c r="DL34" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="DM34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="DN34" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="DO34" t="n">
-        <v>7</v>
-      </c>
       <c r="DP34" t="b">
         <v>1</v>
       </c>
@@ -15946,64 +15938,52 @@
       </c>
       <c r="DW34" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="DX34" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="DY34" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="DZ34" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="EA34" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EB34" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="EC34" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="ED34" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="EE34" t="inlineStr">
         <is>
-          <t>4.02</t>
-        </is>
-      </c>
-      <c r="EF34" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="EG34" t="inlineStr">
-        <is>
-          <t>2.57</t>
-        </is>
-      </c>
-      <c r="EH34" t="inlineStr">
-        <is>
-          <t>1.20</t>
-        </is>
-      </c>
+          <t>3.74</t>
+        </is>
+      </c>
+      <c r="EF34" t="inlineStr"/>
+      <c r="EG34" t="inlineStr"/>
+      <c r="EH34" t="inlineStr"/>
       <c r="EI34" t="inlineStr"/>
       <c r="EJ34" t="inlineStr"/>
     </row>
@@ -16023,12 +16003,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F35" s="1" t="n">
@@ -16044,13 +16024,13 @@
         <v>1</v>
       </c>
       <c r="J35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K35" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L35" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M35" t="n">
         <v>2</v>
@@ -16065,37 +16045,45 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="U35" t="n">
         <v>5</v>
       </c>
       <c r="V35" t="n">
+        <v>22</v>
+      </c>
+      <c r="W35" t="n">
+        <v>13</v>
+      </c>
+      <c r="X35" t="n">
         <v>11</v>
       </c>
-      <c r="W35" t="n">
-        <v>17</v>
-      </c>
-      <c r="X35" t="n">
-        <v>16</v>
-      </c>
       <c r="Y35" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="Z35" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA35" t="inlineStr"/>
-      <c r="AB35" t="inlineStr"/>
+        <v>67</v>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>Veritas Stadion</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>Hippoksentie 6, Åbo</t>
+        </is>
+      </c>
       <c r="AC35" t="n">
         <v>2</v>
       </c>
@@ -16103,88 +16091,88 @@
         <v>1</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.56</v>
+        <v>4.6</v>
       </c>
       <c r="AF35" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.44</v>
+        <v>1.6</v>
       </c>
       <c r="AH35" t="n">
         <v>1.19</v>
       </c>
       <c r="AI35" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AK35" t="n">
         <v>1.67</v>
       </c>
-      <c r="AJ35" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AL35" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.87</v>
+        <v>1.63</v>
       </c>
       <c r="AO35" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="AP35" t="n">
-        <v>2.12</v>
+        <v>2.43</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AR35" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AS35" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="AT35" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AU35" t="n">
         <v>1</v>
       </c>
       <c r="AV35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW35" t="n">
         <v>0</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY35" t="n">
         <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="BC35" t="n">
         <v>0</v>
       </c>
       <c r="BD35" t="n">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="BE35" t="n">
         <v>0</v>
       </c>
       <c r="BF35" t="n">
-        <v>4308</v>
+        <v>3547</v>
       </c>
       <c r="BG35" t="n">
         <v>2</v>
@@ -16193,22 +16181,22 @@
         <v>1</v>
       </c>
       <c r="BI35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BJ35" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BK35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BL35" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BM35" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="BN35" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BO35" t="n">
         <v>1</v>
@@ -16232,25 +16220,25 @@
         <v>1</v>
       </c>
       <c r="BV35" t="n">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="BW35" t="n">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="BX35" t="n">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="BY35" t="n">
         <v>131</v>
       </c>
       <c r="BZ35" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="CA35" t="n">
-        <v>1.17</v>
+        <v>2.31</v>
       </c>
       <c r="CB35" t="n">
-        <v>1.92</v>
+        <v>3.11</v>
       </c>
       <c r="CC35" t="n">
         <v>0</v>
@@ -16286,10 +16274,10 @@
         <v>0</v>
       </c>
       <c r="CN35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP35" t="n">
         <v>0</v>
@@ -16298,73 +16286,73 @@
         <v>1</v>
       </c>
       <c r="CR35" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="CS35" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="CT35" t="n">
         <v>1</v>
       </c>
       <c r="CU35" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="CV35" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW35" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX35" t="n">
+        <v>19</v>
+      </c>
+      <c r="CY35" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ35" t="n">
+        <v>33</v>
+      </c>
+      <c r="DA35" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB35" t="n">
         <v>17</v>
       </c>
-      <c r="CW35" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX35" t="n">
-        <v>11</v>
-      </c>
-      <c r="CY35" t="n">
-        <v>7</v>
-      </c>
-      <c r="CZ35" t="n">
-        <v>88</v>
-      </c>
-      <c r="DA35" t="n">
-        <v>88</v>
-      </c>
-      <c r="DB35" t="n">
-        <v>88</v>
-      </c>
       <c r="DC35" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="DD35" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="DE35" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="DF35" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="DG35" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DH35" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="DI35" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="DJ35" t="n">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="DK35" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="DL35" t="n">
-        <v>1.74</v>
+        <v>1.47</v>
       </c>
       <c r="DM35" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="DN35" t="n">
-        <v>3.17</v>
+        <v>2.48</v>
       </c>
       <c r="DO35" t="n">
         <v>8</v>
@@ -16392,52 +16380,64 @@
       </c>
       <c r="DW35" t="inlineStr">
         <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="DX35" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="DY35" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="DZ35" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EA35" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EB35" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="EC35" t="inlineStr">
+        <is>
           <t>1.74</t>
         </is>
       </c>
-      <c r="DX35" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
-      <c r="DY35" t="inlineStr">
+      <c r="ED35" t="inlineStr">
+        <is>
+          <t>4.73</t>
+        </is>
+      </c>
+      <c r="EE35" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
+      </c>
+      <c r="EF35" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EG35" t="inlineStr">
         <is>
           <t>2.57</t>
         </is>
       </c>
-      <c r="DZ35" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="EA35" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="EB35" t="inlineStr">
-        <is>
-          <t>3.32</t>
-        </is>
-      </c>
-      <c r="EC35" t="inlineStr">
-        <is>
-          <t>2.22</t>
-        </is>
-      </c>
-      <c r="ED35" t="inlineStr">
-        <is>
-          <t>3.16</t>
-        </is>
-      </c>
-      <c r="EE35" t="inlineStr">
-        <is>
-          <t>3.74</t>
-        </is>
-      </c>
-      <c r="EF35" t="inlineStr"/>
-      <c r="EG35" t="inlineStr"/>
-      <c r="EH35" t="inlineStr"/>
+      <c r="EH35" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
       <c r="EI35" t="inlineStr"/>
       <c r="EJ35" t="inlineStr"/>
     </row>
@@ -16776,7 +16776,7 @@
         <v>84</v>
       </c>
       <c r="DD36" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="DE36" t="n">
         <v>0.33</v>
@@ -16809,7 +16809,7 @@
         <v>3.33</v>
       </c>
       <c r="DO36" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP36" t="b">
         <v>0</v>
@@ -17202,7 +17202,7 @@
         <v>50</v>
       </c>
       <c r="DD37" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="DE37" t="n">
         <v>0.4</v>
@@ -17235,7 +17235,7 @@
         <v>3.8</v>
       </c>
       <c r="DO37" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -17648,10 +17648,10 @@
         <v>25</v>
       </c>
       <c r="DD38" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="DE38" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="DF38" t="n">
         <v>2</v>
@@ -17681,7 +17681,7 @@
         <v>2.63</v>
       </c>
       <c r="DO38" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -18097,7 +18097,7 @@
         <v>1.25</v>
       </c>
       <c r="DE39" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DF39" t="n">
         <v>1.5</v>
@@ -18127,7 +18127,7 @@
         <v>1.68</v>
       </c>
       <c r="DO39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -18557,7 +18557,7 @@
         <v>2.58</v>
       </c>
       <c r="DO40" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -18962,7 +18962,7 @@
         <v>75</v>
       </c>
       <c r="DD41" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="DE41" t="n">
         <v>2.25</v>
@@ -18995,7 +18995,7 @@
         <v>3.38</v>
       </c>
       <c r="DO41" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -19441,7 +19441,7 @@
         <v>2.47</v>
       </c>
       <c r="DO42" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -19895,7 +19895,7 @@
         <v>2.52</v>
       </c>
       <c r="DO43" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -20307,7 +20307,7 @@
         <v>3</v>
       </c>
       <c r="DE44" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="DF44" t="n">
         <v>3</v>
@@ -20337,7 +20337,7 @@
         <v>2.86</v>
       </c>
       <c r="DO44" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -20759,7 +20759,7 @@
         <v>2.59</v>
       </c>
       <c r="DO45" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -20885,10 +20885,10 @@
         <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L46" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M46" t="n">
         <v>1</v>
@@ -20906,19 +20906,19 @@
         <v>2</v>
       </c>
       <c r="R46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T46" t="n">
         <v>4</v>
       </c>
       <c r="U46" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V46" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W46" t="n">
         <v>12</v>
@@ -20927,10 +20927,10 @@
         <v>10</v>
       </c>
       <c r="Y46" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Z46" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AA46" t="inlineStr"/>
       <c r="AB46" t="inlineStr"/>
@@ -21082,13 +21082,13 @@
         <v>105</v>
       </c>
       <c r="BZ46" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="CA46" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="CB46" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="CC46" t="n">
         <v>0</v>
@@ -21136,19 +21136,19 @@
         <v>1</v>
       </c>
       <c r="CR46" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CS46" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="CT46" t="n">
         <v>1</v>
       </c>
       <c r="CU46" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="CV46" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="CW46" t="n">
         <v>1</v>
@@ -21172,7 +21172,7 @@
         <v>84</v>
       </c>
       <c r="DD46" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="DE46" t="n">
         <v>2.25</v>
@@ -21205,7 +21205,7 @@
         <v>2.58</v>
       </c>
       <c r="DO46" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -21342,13 +21342,13 @@
         <v>7</v>
       </c>
       <c r="T47" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U47" t="n">
         <v>12</v>
       </c>
       <c r="V47" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W47" t="n">
         <v>12</v>
@@ -21357,10 +21357,10 @@
         <v>9</v>
       </c>
       <c r="Y47" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="Z47" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
@@ -21523,10 +21523,10 @@
         <v>1.53</v>
       </c>
       <c r="CA47" t="n">
-        <v>0.95</v>
+        <v>0.83</v>
       </c>
       <c r="CB47" t="n">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="CC47" t="n">
         <v>0</v>
@@ -21583,10 +21583,10 @@
         <v>1</v>
       </c>
       <c r="CU47" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="CV47" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="CW47" t="n">
         <v>1</v>
@@ -21595,7 +21595,7 @@
         <v>8</v>
       </c>
       <c r="CY47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CZ47" t="n">
         <v>25</v>
@@ -21610,7 +21610,7 @@
         <v>63</v>
       </c>
       <c r="DD47" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="DE47" t="n">
         <v>0.4</v>
@@ -21643,7 +21643,7 @@
         <v>3.63</v>
       </c>
       <c r="DO47" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -21728,6 +21728,2610 @@
       </c>
       <c r="EI47" t="inlineStr"/>
       <c r="EJ47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Finland_Veikkausliiga_2026</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>8</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VPS</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>HJK</t>
+        </is>
+      </c>
+      <c r="F48" s="1" t="n">
+        <v>46164.66666666666</v>
+      </c>
+      <c r="G48" t="n">
+        <v>2</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" t="n">
+        <v>3</v>
+      </c>
+      <c r="J48" t="n">
+        <v>5</v>
+      </c>
+      <c r="K48" t="n">
+        <v>4</v>
+      </c>
+      <c r="L48" t="n">
+        <v>9</v>
+      </c>
+      <c r="M48" t="n">
+        <v>5</v>
+      </c>
+      <c r="N48" t="n">
+        <v>1</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>5</v>
+      </c>
+      <c r="R48" t="n">
+        <v>2</v>
+      </c>
+      <c r="S48" t="n">
+        <v>8</v>
+      </c>
+      <c r="T48" t="n">
+        <v>11</v>
+      </c>
+      <c r="U48" t="n">
+        <v>13</v>
+      </c>
+      <c r="V48" t="n">
+        <v>13</v>
+      </c>
+      <c r="W48" t="n">
+        <v>23</v>
+      </c>
+      <c r="X48" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>43</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>57</v>
+      </c>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>408</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD48" t="n">
+        <v>59</v>
+      </c>
+      <c r="BE48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF48" t="n">
+        <v>3109</v>
+      </c>
+      <c r="BG48" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH48" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI48" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ48" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK48" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL48" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM48" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN48" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO48" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ48" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR48" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS48" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT48" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU48" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV48" t="n">
+        <v>44</v>
+      </c>
+      <c r="BW48" t="n">
+        <v>29</v>
+      </c>
+      <c r="BX48" t="n">
+        <v>111</v>
+      </c>
+      <c r="BY48" t="n">
+        <v>76</v>
+      </c>
+      <c r="BZ48" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CA48" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="CB48" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="CC48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR48" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS48" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU48" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV48" t="n">
+        <v>23</v>
+      </c>
+      <c r="CW48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX48" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY48" t="n">
+        <v>11</v>
+      </c>
+      <c r="CZ48" t="n">
+        <v>29</v>
+      </c>
+      <c r="DA48" t="n">
+        <v>71</v>
+      </c>
+      <c r="DB48" t="n">
+        <v>29</v>
+      </c>
+      <c r="DC48" t="n">
+        <v>71</v>
+      </c>
+      <c r="DD48" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE48" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF48" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DG48" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DH48" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DI48" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DJ48" t="n">
+        <v>71</v>
+      </c>
+      <c r="DK48" t="n">
+        <v>29</v>
+      </c>
+      <c r="DL48" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="DM48" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DN48" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="DO48" t="n">
+        <v>8</v>
+      </c>
+      <c r="DP48" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ48" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR48" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS48" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT48" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU48" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV48" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW48" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="DX48" t="inlineStr">
+        <is>
+          <t>2.47</t>
+        </is>
+      </c>
+      <c r="DY48" t="inlineStr"/>
+      <c r="DZ48" t="inlineStr"/>
+      <c r="EA48" t="inlineStr"/>
+      <c r="EB48" t="inlineStr"/>
+      <c r="EC48" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="ED48" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="EE48" t="inlineStr">
+        <is>
+          <t>3.73</t>
+        </is>
+      </c>
+      <c r="EF48" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EG48" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="EH48" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="EI48" t="inlineStr"/>
+      <c r="EJ48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Finland_Veikkausliiga_2026</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>8</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Inter Turku</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>TPS</t>
+        </is>
+      </c>
+      <c r="F49" s="1" t="n">
+        <v>46165.45833333334</v>
+      </c>
+      <c r="G49" t="n">
+        <v>2</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" t="n">
+        <v>3</v>
+      </c>
+      <c r="J49" t="n">
+        <v>5</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1</v>
+      </c>
+      <c r="L49" t="n">
+        <v>6</v>
+      </c>
+      <c r="M49" t="n">
+        <v>3</v>
+      </c>
+      <c r="N49" t="n">
+        <v>2</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>6</v>
+      </c>
+      <c r="R49" t="n">
+        <v>2</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="n">
+        <v>7</v>
+      </c>
+      <c r="U49" t="n">
+        <v>16</v>
+      </c>
+      <c r="V49" t="n">
+        <v>9</v>
+      </c>
+      <c r="W49" t="n">
+        <v>16</v>
+      </c>
+      <c r="X49" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>58</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>Veritas Stadion</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>Hippoksentie 6, Åbo</t>
+        </is>
+      </c>
+      <c r="AC49" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>406</v>
+      </c>
+      <c r="BC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD49" t="n">
+        <v>54</v>
+      </c>
+      <c r="BE49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF49" t="n">
+        <v>8102</v>
+      </c>
+      <c r="BG49" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH49" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI49" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK49" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL49" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM49" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN49" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO49" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ49" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR49" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS49" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT49" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU49" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV49" t="n">
+        <v>78</v>
+      </c>
+      <c r="BW49" t="n">
+        <v>61</v>
+      </c>
+      <c r="BX49" t="n">
+        <v>138</v>
+      </c>
+      <c r="BY49" t="n">
+        <v>104</v>
+      </c>
+      <c r="BZ49" t="n">
+        <v>2</v>
+      </c>
+      <c r="CA49" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="CB49" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="CC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI49" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ49" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM49" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ49" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR49" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS49" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT49" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU49" t="n">
+        <v>2</v>
+      </c>
+      <c r="CV49" t="n">
+        <v>5</v>
+      </c>
+      <c r="CW49" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX49" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY49" t="n">
+        <v>13</v>
+      </c>
+      <c r="CZ49" t="n">
+        <v>27</v>
+      </c>
+      <c r="DA49" t="n">
+        <v>64</v>
+      </c>
+      <c r="DB49" t="n">
+        <v>37</v>
+      </c>
+      <c r="DC49" t="n">
+        <v>64</v>
+      </c>
+      <c r="DD49" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DE49" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DF49" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DG49" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DH49" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="DI49" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DJ49" t="n">
+        <v>74</v>
+      </c>
+      <c r="DK49" t="n">
+        <v>37</v>
+      </c>
+      <c r="DL49" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="DM49" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DN49" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="DO49" t="n">
+        <v>8</v>
+      </c>
+      <c r="DP49" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ49" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR49" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS49" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT49" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU49" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV49" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW49" t="inlineStr"/>
+      <c r="DX49" t="inlineStr"/>
+      <c r="DY49" t="inlineStr">
+        <is>
+          <t>2.73</t>
+        </is>
+      </c>
+      <c r="DZ49" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EA49" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EB49" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="EC49" t="inlineStr">
+        <is>
+          <t>6.08</t>
+        </is>
+      </c>
+      <c r="ED49" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EE49" t="inlineStr">
+        <is>
+          <t>4.24</t>
+        </is>
+      </c>
+      <c r="EF49" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EG49" t="inlineStr">
+        <is>
+          <t>3.07</t>
+        </is>
+      </c>
+      <c r="EH49" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="EI49" t="inlineStr"/>
+      <c r="EJ49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Finland_Veikkausliiga_2026</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>8</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>KuPS</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Lahti</t>
+        </is>
+      </c>
+      <c r="F50" s="1" t="n">
+        <v>46165.58333333334</v>
+      </c>
+      <c r="G50" t="n">
+        <v>2</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" t="n">
+        <v>3</v>
+      </c>
+      <c r="J50" t="n">
+        <v>9</v>
+      </c>
+      <c r="K50" t="n">
+        <v>2</v>
+      </c>
+      <c r="L50" t="n">
+        <v>11</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>4</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>3</v>
+      </c>
+      <c r="R50" t="n">
+        <v>4</v>
+      </c>
+      <c r="S50" t="n">
+        <v>15</v>
+      </c>
+      <c r="T50" t="n">
+        <v>5</v>
+      </c>
+      <c r="U50" t="n">
+        <v>18</v>
+      </c>
+      <c r="V50" t="n">
+        <v>9</v>
+      </c>
+      <c r="W50" t="n">
+        <v>13</v>
+      </c>
+      <c r="X50" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>49</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>51</v>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>Savon Sanomat Areena</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>Kaartokatu 6, Kuopio</t>
+        </is>
+      </c>
+      <c r="AC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>411</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD50" t="n">
+        <v>37</v>
+      </c>
+      <c r="BE50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF50" t="n">
+        <v>2882</v>
+      </c>
+      <c r="BG50" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH50" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI50" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ50" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK50" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL50" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM50" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN50" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP50" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR50" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS50" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT50" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU50" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV50" t="n">
+        <v>64</v>
+      </c>
+      <c r="BW50" t="n">
+        <v>26</v>
+      </c>
+      <c r="BX50" t="n">
+        <v>80</v>
+      </c>
+      <c r="BY50" t="n">
+        <v>70</v>
+      </c>
+      <c r="BZ50" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA50" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB50" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="CC50" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE50" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI50" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ50" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL50" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM50" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ50" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR50" t="n">
+        <v>26</v>
+      </c>
+      <c r="CS50" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT50" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU50" t="n">
+        <v>3</v>
+      </c>
+      <c r="CV50" t="n">
+        <v>1</v>
+      </c>
+      <c r="CW50" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX50" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY50" t="n">
+        <v>13</v>
+      </c>
+      <c r="CZ50" t="n">
+        <v>37</v>
+      </c>
+      <c r="DA50" t="n">
+        <v>47</v>
+      </c>
+      <c r="DB50" t="n">
+        <v>10</v>
+      </c>
+      <c r="DC50" t="n">
+        <v>80</v>
+      </c>
+      <c r="DD50" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DE50" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DF50" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DG50" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH50" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DI50" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DJ50" t="n">
+        <v>64</v>
+      </c>
+      <c r="DK50" t="n">
+        <v>54</v>
+      </c>
+      <c r="DL50" t="n">
+        <v>2</v>
+      </c>
+      <c r="DM50" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DN50" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="DO50" t="n">
+        <v>8</v>
+      </c>
+      <c r="DP50" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ50" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR50" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS50" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT50" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU50" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV50" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW50" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="DX50" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="DY50" t="inlineStr"/>
+      <c r="DZ50" t="inlineStr"/>
+      <c r="EA50" t="inlineStr"/>
+      <c r="EB50" t="inlineStr"/>
+      <c r="EC50" t="inlineStr">
+        <is>
+          <t>6.64</t>
+        </is>
+      </c>
+      <c r="ED50" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EE50" t="inlineStr">
+        <is>
+          <t>4.38</t>
+        </is>
+      </c>
+      <c r="EF50" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EG50" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="EH50" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="EI50" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EJ50" t="inlineStr">
+        <is>
+          <t>2.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Finland_Veikkausliiga_2026</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>8</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Jaro</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Mariehamn</t>
+        </is>
+      </c>
+      <c r="F51" s="1" t="n">
+        <v>46165.58333333334</v>
+      </c>
+      <c r="G51" t="n">
+        <v>3</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>3</v>
+      </c>
+      <c r="J51" t="n">
+        <v>2</v>
+      </c>
+      <c r="K51" t="n">
+        <v>4</v>
+      </c>
+      <c r="L51" t="n">
+        <v>6</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1</v>
+      </c>
+      <c r="N51" t="n">
+        <v>2</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>9</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1</v>
+      </c>
+      <c r="S51" t="n">
+        <v>6</v>
+      </c>
+      <c r="T51" t="n">
+        <v>5</v>
+      </c>
+      <c r="U51" t="n">
+        <v>15</v>
+      </c>
+      <c r="V51" t="n">
+        <v>6</v>
+      </c>
+      <c r="W51" t="n">
+        <v>19</v>
+      </c>
+      <c r="X51" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>43</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>57</v>
+      </c>
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr"/>
+      <c r="AC51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>416</v>
+      </c>
+      <c r="BC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD51" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF51" t="n">
+        <v>1826</v>
+      </c>
+      <c r="BG51" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH51" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI51" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ51" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK51" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL51" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM51" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN51" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP51" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ51" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR51" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS51" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT51" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU51" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV51" t="n">
+        <v>72</v>
+      </c>
+      <c r="BW51" t="n">
+        <v>61</v>
+      </c>
+      <c r="BX51" t="n">
+        <v>91</v>
+      </c>
+      <c r="BY51" t="n">
+        <v>104</v>
+      </c>
+      <c r="BZ51" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="CA51" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CB51" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="CC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI51" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ51" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK51" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ51" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR51" t="n">
+        <v>27</v>
+      </c>
+      <c r="CS51" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT51" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU51" t="n">
+        <v>2</v>
+      </c>
+      <c r="CV51" t="n">
+        <v>4</v>
+      </c>
+      <c r="CW51" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX51" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY51" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ51" t="n">
+        <v>33</v>
+      </c>
+      <c r="DA51" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB51" t="n">
+        <v>17</v>
+      </c>
+      <c r="DC51" t="n">
+        <v>84</v>
+      </c>
+      <c r="DD51" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DE51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DF51" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DG51" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DH51" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DI51" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="DJ51" t="n">
+        <v>67</v>
+      </c>
+      <c r="DK51" t="n">
+        <v>33</v>
+      </c>
+      <c r="DL51" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="DM51" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="DN51" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DO51" t="n">
+        <v>8</v>
+      </c>
+      <c r="DP51" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ51" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR51" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS51" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT51" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU51" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV51" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW51" t="inlineStr"/>
+      <c r="DX51" t="inlineStr"/>
+      <c r="DY51" t="inlineStr"/>
+      <c r="DZ51" t="inlineStr"/>
+      <c r="EA51" t="inlineStr"/>
+      <c r="EB51" t="inlineStr"/>
+      <c r="EC51" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="ED51" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EE51" t="inlineStr">
+        <is>
+          <t>3.78</t>
+        </is>
+      </c>
+      <c r="EF51" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EG51" t="inlineStr">
+        <is>
+          <t>3.47</t>
+        </is>
+      </c>
+      <c r="EH51" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EI51" t="inlineStr"/>
+      <c r="EJ51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Finland_Veikkausliiga_2026</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>8</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>SJK</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Oulu</t>
+        </is>
+      </c>
+      <c r="F52" s="1" t="n">
+        <v>46165.58333333334</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" t="n">
+        <v>7</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1</v>
+      </c>
+      <c r="L52" t="n">
+        <v>8</v>
+      </c>
+      <c r="M52" t="n">
+        <v>1</v>
+      </c>
+      <c r="N52" t="n">
+        <v>1</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>5</v>
+      </c>
+      <c r="R52" t="n">
+        <v>4</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>15</v>
+      </c>
+      <c r="V52" t="n">
+        <v>7</v>
+      </c>
+      <c r="W52" t="n">
+        <v>13</v>
+      </c>
+      <c r="X52" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>69</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>31</v>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>OmaSP Stadion</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>Alaseinäjoenkatu 9, Seinäjoki</t>
+        </is>
+      </c>
+      <c r="AC52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AQ52" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR52" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT52" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AU52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA52" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB52" t="n">
+        <v>425</v>
+      </c>
+      <c r="BC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD52" t="n">
+        <v>68</v>
+      </c>
+      <c r="BE52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF52" t="n">
+        <v>4568</v>
+      </c>
+      <c r="BG52" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH52" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI52" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ52" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK52" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM52" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN52" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ52" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR52" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT52" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU52" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV52" t="n">
+        <v>77</v>
+      </c>
+      <c r="BW52" t="n">
+        <v>11</v>
+      </c>
+      <c r="BX52" t="n">
+        <v>145</v>
+      </c>
+      <c r="BY52" t="n">
+        <v>44</v>
+      </c>
+      <c r="BZ52" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="CA52" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CB52" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="CC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI52" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ52" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ52" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR52" t="n">
+        <v>24</v>
+      </c>
+      <c r="CS52" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT52" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU52" t="n">
+        <v>6</v>
+      </c>
+      <c r="CV52" t="n">
+        <v>2</v>
+      </c>
+      <c r="CW52" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX52" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY52" t="n">
+        <v>19</v>
+      </c>
+      <c r="CZ52" t="n">
+        <v>55</v>
+      </c>
+      <c r="DA52" t="n">
+        <v>80</v>
+      </c>
+      <c r="DB52" t="n">
+        <v>43</v>
+      </c>
+      <c r="DC52" t="n">
+        <v>100</v>
+      </c>
+      <c r="DD52" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE52" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DF52" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DG52" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DH52" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DI52" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DJ52" t="n">
+        <v>45</v>
+      </c>
+      <c r="DK52" t="n">
+        <v>20</v>
+      </c>
+      <c r="DL52" t="n">
+        <v>2</v>
+      </c>
+      <c r="DM52" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DN52" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="DO52" t="n">
+        <v>8</v>
+      </c>
+      <c r="DP52" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ52" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR52" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS52" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT52" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU52" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV52" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW52" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="DX52" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="DY52" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="DZ52" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EA52" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EB52" t="inlineStr">
+        <is>
+          <t>3.32</t>
+        </is>
+      </c>
+      <c r="EC52" t="inlineStr">
+        <is>
+          <t>2.77</t>
+        </is>
+      </c>
+      <c r="ED52" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="EE52" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="EF52" t="inlineStr"/>
+      <c r="EG52" t="inlineStr"/>
+      <c r="EH52" t="inlineStr"/>
+      <c r="EI52" t="inlineStr"/>
+      <c r="EJ52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Finland_Veikkausliiga_2026</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>8</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Ilves</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Gnistan</t>
+        </is>
+      </c>
+      <c r="F53" s="1" t="n">
+        <v>46165.58333333334</v>
+      </c>
+      <c r="G53" t="n">
+        <v>2</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>2</v>
+      </c>
+      <c r="J53" t="n">
+        <v>5</v>
+      </c>
+      <c r="K53" t="n">
+        <v>4</v>
+      </c>
+      <c r="L53" t="n">
+        <v>9</v>
+      </c>
+      <c r="M53" t="n">
+        <v>3</v>
+      </c>
+      <c r="N53" t="n">
+        <v>2</v>
+      </c>
+      <c r="O53" t="n">
+        <v>1</v>
+      </c>
+      <c r="P53" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>3</v>
+      </c>
+      <c r="R53" t="n">
+        <v>3</v>
+      </c>
+      <c r="S53" t="n">
+        <v>6</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>9</v>
+      </c>
+      <c r="V53" t="n">
+        <v>6</v>
+      </c>
+      <c r="W53" t="n">
+        <v>11</v>
+      </c>
+      <c r="X53" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>57</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>43</v>
+      </c>
+      <c r="AA53" t="inlineStr"/>
+      <c r="AB53" t="inlineStr"/>
+      <c r="AC53" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ53" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA53" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB53" t="n">
+        <v>407</v>
+      </c>
+      <c r="BC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD53" t="n">
+        <v>67</v>
+      </c>
+      <c r="BE53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF53" t="n">
+        <v>4003</v>
+      </c>
+      <c r="BG53" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH53" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI53" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK53" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL53" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM53" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN53" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ53" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR53" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT53" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU53" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV53" t="n">
+        <v>47</v>
+      </c>
+      <c r="BW53" t="n">
+        <v>58</v>
+      </c>
+      <c r="BX53" t="n">
+        <v>86</v>
+      </c>
+      <c r="BY53" t="n">
+        <v>88</v>
+      </c>
+      <c r="BZ53" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="CA53" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB53" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="CC53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR53" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS53" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CV53" t="n">
+        <v>2</v>
+      </c>
+      <c r="CW53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX53" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY53" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ53" t="n">
+        <v>34</v>
+      </c>
+      <c r="DA53" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB53" t="n">
+        <v>34</v>
+      </c>
+      <c r="DC53" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD53" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE53" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DF53" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG53" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DH53" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DI53" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DJ53" t="n">
+        <v>67</v>
+      </c>
+      <c r="DK53" t="n">
+        <v>33</v>
+      </c>
+      <c r="DL53" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DM53" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="DN53" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="DO53" t="n">
+        <v>8</v>
+      </c>
+      <c r="DP53" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ53" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR53" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS53" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT53" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU53" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV53" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW53" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="DX53" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="DY53" t="inlineStr"/>
+      <c r="DZ53" t="inlineStr"/>
+      <c r="EA53" t="inlineStr"/>
+      <c r="EB53" t="inlineStr"/>
+      <c r="EC53" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
+      <c r="ED53" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EE53" t="inlineStr">
+        <is>
+          <t>3.74</t>
+        </is>
+      </c>
+      <c r="EF53" t="inlineStr"/>
+      <c r="EG53" t="inlineStr"/>
+      <c r="EH53" t="inlineStr"/>
+      <c r="EI53" t="inlineStr"/>
+      <c r="EJ53" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Finland_Veikkausliiga_2026.xlsx
+++ b/data/matches/leagues/Finland_Veikkausliiga_2026.xlsx
@@ -595,8 +595,8 @@
     <col width="16.8" customWidth="1" min="24" max="24"/>
     <col width="22.8" customWidth="1" min="25" max="25"/>
     <col width="22.8" customWidth="1" min="26" max="26"/>
-    <col width="26.4" customWidth="1" min="27" max="27"/>
-    <col width="38.4" customWidth="1" min="28" max="28"/>
+    <col width="16.8" customWidth="1" min="27" max="27"/>
+    <col width="21.6" customWidth="1" min="28" max="28"/>
     <col width="21.6" customWidth="1" min="29" max="29"/>
     <col width="21.6" customWidth="1" min="30" max="30"/>
     <col width="18" customWidth="1" min="31" max="31"/>
@@ -1500,16 +1500,8 @@
       <c r="Z2" t="n">
         <v>33</v>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Veritas Stadion</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Hippoksentie 6, Åbo</t>
-        </is>
-      </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
         <v>1</v>
       </c>
@@ -3666,16 +3658,8 @@
       <c r="Z7" t="n">
         <v>51</v>
       </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Mustapekka Areena</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Käskynhaltijantie 11, Helsinki</t>
-        </is>
-      </c>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="n">
         <v>1</v>
       </c>
@@ -4112,16 +4096,8 @@
       <c r="Z8" t="n">
         <v>61</v>
       </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Veritas Stadion</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Hippoksentie 6, Åbo</t>
-        </is>
-      </c>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="n">
         <v>3</v>
       </c>
@@ -4574,16 +4550,8 @@
       <c r="Z9" t="n">
         <v>47</v>
       </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>OmaSP Stadion</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Alaseinäjoenkatu 9, Seinäjoki</t>
-        </is>
-      </c>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="n">
         <v>0</v>
       </c>
@@ -5466,16 +5434,8 @@
       <c r="Z11" t="n">
         <v>29</v>
       </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Savon Sanomat Areena</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Kaartokatu 6, Kuopio</t>
-        </is>
-      </c>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="n">
         <v>0</v>
       </c>
@@ -6350,16 +6310,8 @@
       <c r="Z13" t="n">
         <v>36</v>
       </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Veritas Stadion</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Hippoksentie 6, Åbo</t>
-        </is>
-      </c>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="n">
         <v>2</v>
       </c>
@@ -6796,16 +6748,8 @@
       <c r="Z14" t="n">
         <v>55</v>
       </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Mustapekka Areena</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Käskynhaltijantie 11, Helsinki</t>
-        </is>
-      </c>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="n">
         <v>3</v>
       </c>
@@ -7672,16 +7616,8 @@
       <c r="Z16" t="n">
         <v>48</v>
       </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Raatin stadion</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Raatintie 2, Koskikeskus, Oulu</t>
-        </is>
-      </c>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="n">
         <v>2</v>
       </c>
@@ -8588,16 +8524,8 @@
       <c r="Z18" t="n">
         <v>55</v>
       </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Veritas Stadion</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Hippoksentie 6, Åbo</t>
-        </is>
-      </c>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="n">
         <v>2</v>
       </c>
@@ -9456,16 +9384,8 @@
       <c r="Z20" t="n">
         <v>43</v>
       </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>Savon Sanomat Areena</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>Kaartokatu 6, Kuopio</t>
-        </is>
-      </c>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="n">
         <v>0</v>
       </c>
@@ -10340,16 +10260,8 @@
       <c r="Z22" t="n">
         <v>36</v>
       </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>Veritas Stadion</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>Hippoksentie 6, Åbo</t>
-        </is>
-      </c>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="n">
         <v>3</v>
       </c>
@@ -10786,16 +10698,8 @@
       <c r="Z23" t="n">
         <v>41</v>
       </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>OmaSP Stadion</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>Alaseinäjoenkatu 9, Seinäjoki</t>
-        </is>
-      </c>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="n">
         <v>1</v>
       </c>
@@ -11678,16 +11582,8 @@
       <c r="Z25" t="n">
         <v>46</v>
       </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>Veritas Stadion</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>Hippoksentie 6, Åbo</t>
-        </is>
-      </c>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="n">
         <v>1</v>
       </c>
@@ -12124,16 +12020,8 @@
       <c r="Z26" t="n">
         <v>43</v>
       </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>Savon Sanomat Areena</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>Kaartokatu 6, Kuopio</t>
-        </is>
-      </c>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="n">
         <v>1</v>
       </c>
@@ -12554,16 +12442,8 @@
       <c r="Z27" t="n">
         <v>37</v>
       </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>Veritas Stadion</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>Hippoksentie 6, Åbo</t>
-        </is>
-      </c>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="n">
         <v>2</v>
       </c>
@@ -13000,16 +12880,8 @@
       <c r="Z28" t="n">
         <v>44</v>
       </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>OmaSP Stadion</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>Alaseinäjoenkatu 9, Seinäjoki</t>
-        </is>
-      </c>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="n">
         <v>1</v>
       </c>
@@ -14314,16 +14186,8 @@
       <c r="Z31" t="n">
         <v>68</v>
       </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>Raatin stadion</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>Raatintie 2, Koskikeskus, Oulu</t>
-        </is>
-      </c>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="n">
         <v>1</v>
       </c>
@@ -15214,16 +15078,8 @@
       <c r="Z33" t="n">
         <v>69</v>
       </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>Mustapekka Areena</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>Käskynhaltijantie 11, Helsinki</t>
-        </is>
-      </c>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="n">
         <v>2</v>
       </c>
@@ -16074,16 +15930,8 @@
       <c r="Z35" t="n">
         <v>67</v>
       </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>Veritas Stadion</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>Hippoksentie 6, Åbo</t>
-        </is>
-      </c>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="n">
         <v>2</v>
       </c>
@@ -16528,16 +16376,8 @@
       <c r="Z36" t="n">
         <v>36</v>
       </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>Savon Sanomat Areena</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>Kaartokatu 6, Kuopio</t>
-        </is>
-      </c>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="n">
         <v>1</v>
       </c>
@@ -16954,16 +16794,8 @@
       <c r="Z37" t="n">
         <v>43</v>
       </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>Veritas Stadion</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>Hippoksentie 6, Åbo</t>
-        </is>
-      </c>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="n">
         <v>2</v>
       </c>
@@ -18714,16 +18546,8 @@
       <c r="Z41" t="n">
         <v>47</v>
       </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>OmaSP Stadion</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>Alaseinäjoenkatu 9, Seinäjoki</t>
-        </is>
-      </c>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="n">
         <v>2</v>
       </c>
@@ -19614,16 +19438,8 @@
       <c r="Z43" t="n">
         <v>52</v>
       </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>Mustapekka Areena</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>Käskynhaltijantie 11, Helsinki</t>
-        </is>
-      </c>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="n">
         <v>1</v>
       </c>
@@ -20056,16 +19872,8 @@
       <c r="Z44" t="n">
         <v>51</v>
       </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>Raatin stadion</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>Raatintie 2, Koskikeskus, Oulu</t>
-        </is>
-      </c>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="n">
         <v>4</v>
       </c>
@@ -21362,16 +21170,8 @@
       <c r="Z47" t="n">
         <v>47</v>
       </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>Savon Sanomat Areena</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>Kaartokatu 6, Kuopio</t>
-        </is>
-      </c>
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="n">
         <v>0</v>
       </c>
@@ -21796,13 +21596,13 @@
         <v>8</v>
       </c>
       <c r="T48" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U48" t="n">
         <v>13</v>
       </c>
       <c r="V48" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W48" t="n">
         <v>23</v>
@@ -21811,10 +21611,10 @@
         <v>13</v>
       </c>
       <c r="Y48" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Z48" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AA48" t="inlineStr"/>
       <c r="AB48" t="inlineStr"/>
@@ -21969,10 +21769,10 @@
         <v>1.5</v>
       </c>
       <c r="CA48" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="CB48" t="n">
-        <v>2.67</v>
+        <v>2.73</v>
       </c>
       <c r="CC48" t="n">
         <v>1</v>
@@ -22038,7 +21838,7 @@
         <v>1</v>
       </c>
       <c r="CX48" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CY48" t="n">
         <v>11</v>
@@ -22246,16 +22046,8 @@
       <c r="Z49" t="n">
         <v>42</v>
       </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>Veritas Stadion</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>Hippoksentie 6, Åbo</t>
-        </is>
-      </c>
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="n">
         <v>3</v>
       </c>
@@ -22669,13 +22461,13 @@
         <v>4</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T50" t="n">
         <v>5</v>
       </c>
       <c r="U50" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V50" t="n">
         <v>9</v>
@@ -22692,16 +22484,8 @@
       <c r="Z50" t="n">
         <v>51</v>
       </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>Savon Sanomat Areena</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>Kaartokatu 6, Kuopio</t>
-        </is>
-      </c>
+      <c r="AA50" t="inlineStr"/>
+      <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="n">
         <v>0</v>
       </c>
@@ -22850,13 +22634,13 @@
         <v>70</v>
       </c>
       <c r="BZ50" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="CA50" t="n">
         <v>1.04</v>
       </c>
       <c r="CB50" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="CC50" t="n">
         <v>1</v>
@@ -23540,13 +23324,13 @@
         <v>10</v>
       </c>
       <c r="T52" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U52" t="n">
         <v>15</v>
       </c>
       <c r="V52" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W52" t="n">
         <v>13</v>
@@ -23555,21 +23339,13 @@
         <v>10</v>
       </c>
       <c r="Y52" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="Z52" t="n">
-        <v>31</v>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>OmaSP Stadion</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>Alaseinäjoenkatu 9, Seinäjoki</t>
-        </is>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="n">
         <v>1</v>
       </c>
@@ -23721,10 +23497,10 @@
         <v>1.86</v>
       </c>
       <c r="CA52" t="n">
-        <v>0.8</v>
+        <v>0.93</v>
       </c>
       <c r="CB52" t="n">
-        <v>2.67</v>
+        <v>2.79</v>
       </c>
       <c r="CC52" t="n">
         <v>0</v>
@@ -23781,10 +23557,10 @@
         <v>1</v>
       </c>
       <c r="CU52" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="CV52" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="CW52" t="n">
         <v>1</v>
@@ -23982,13 +23758,13 @@
         <v>6</v>
       </c>
       <c r="T53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U53" t="n">
         <v>9</v>
       </c>
       <c r="V53" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W53" t="n">
         <v>11</v>
@@ -23997,10 +23773,10 @@
         <v>19</v>
       </c>
       <c r="Y53" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="Z53" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="AA53" t="inlineStr"/>
       <c r="AB53" t="inlineStr"/>
@@ -24155,10 +23931,10 @@
         <v>1.12</v>
       </c>
       <c r="CA53" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="CB53" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="CC53" t="n">
         <v>1</v>
@@ -24215,10 +23991,10 @@
         <v>1</v>
       </c>
       <c r="CU53" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="CV53" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="CW53" t="n">
         <v>1</v>

--- a/data/matches/leagues/Finland_Veikkausliiga_2026.xlsx
+++ b/data/matches/leagues/Finland_Veikkausliiga_2026.xlsx
@@ -258,20 +258,20 @@
     <tableColumn id="124" name="over45"/>
     <tableColumn id="125" name="over55"/>
     <tableColumn id="126" name="btts"/>
-    <tableColumn id="127" name="pinnacle_corners_over_95"/>
-    <tableColumn id="128" name="pinnacle_corners_under_95"/>
-    <tableColumn id="129" name="pinnacle_corners_over_85"/>
-    <tableColumn id="130" name="pinnacle_corners_under_85"/>
-    <tableColumn id="131" name="pinnacle_1st_half_over15"/>
-    <tableColumn id="132" name="pinnacle_1st_half_under15"/>
+    <tableColumn id="127" name="pinnacle_ft_over25"/>
+    <tableColumn id="128" name="pinnacle_ft_over15"/>
+    <tableColumn id="129" name="pinnacle_ft_over35"/>
+    <tableColumn id="130" name="pinnacle_1st_half_over15"/>
+    <tableColumn id="131" name="pinnacle_1st_half_under15"/>
+    <tableColumn id="132" name="pinnacle_1st_half_over05"/>
     <tableColumn id="133" name="pinnacle_1st_half_under05"/>
-    <tableColumn id="134" name="pinnacle_1st_half_over05"/>
-    <tableColumn id="135" name="pinnacle_ft_over25"/>
-    <tableColumn id="136" name="pinnacle_ft_over35"/>
-    <tableColumn id="137" name="pinnacle_ft_over15"/>
+    <tableColumn id="134" name="pinnacle_corners_over_95"/>
+    <tableColumn id="135" name="pinnacle_corners_under_95"/>
+    <tableColumn id="136" name="pinnacle_corners_over_85"/>
+    <tableColumn id="137" name="pinnacle_corners_under_85"/>
     <tableColumn id="138" name="pinnacle_ft_x"/>
-    <tableColumn id="139" name="pinnacle_ft_2"/>
-    <tableColumn id="140" name="pinnacle_ft_1"/>
+    <tableColumn id="139" name="pinnacle_ft_1"/>
+    <tableColumn id="140" name="pinnacle_ft_2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -695,17 +695,17 @@
     <col width="9.6" customWidth="1" min="124" max="124"/>
     <col width="9.6" customWidth="1" min="125" max="125"/>
     <col width="8.4" customWidth="1" min="126" max="126"/>
-    <col width="31.2" customWidth="1" min="127" max="127"/>
-    <col width="32.4" customWidth="1" min="128" max="128"/>
-    <col width="31.2" customWidth="1" min="129" max="129"/>
-    <col width="32.4" customWidth="1" min="130" max="130"/>
-    <col width="31.2" customWidth="1" min="131" max="131"/>
-    <col width="32.4" customWidth="1" min="132" max="132"/>
+    <col width="24" customWidth="1" min="127" max="127"/>
+    <col width="24" customWidth="1" min="128" max="128"/>
+    <col width="24" customWidth="1" min="129" max="129"/>
+    <col width="31.2" customWidth="1" min="130" max="130"/>
+    <col width="32.4" customWidth="1" min="131" max="131"/>
+    <col width="31.2" customWidth="1" min="132" max="132"/>
     <col width="32.4" customWidth="1" min="133" max="133"/>
     <col width="31.2" customWidth="1" min="134" max="134"/>
-    <col width="24" customWidth="1" min="135" max="135"/>
-    <col width="24" customWidth="1" min="136" max="136"/>
-    <col width="24" customWidth="1" min="137" max="137"/>
+    <col width="32.4" customWidth="1" min="135" max="135"/>
+    <col width="31.2" customWidth="1" min="136" max="136"/>
+    <col width="32.4" customWidth="1" min="137" max="137"/>
     <col width="18" customWidth="1" min="138" max="138"/>
     <col width="18" customWidth="1" min="139" max="139"/>
     <col width="18" customWidth="1" min="140" max="140"/>
@@ -1344,59 +1344,59 @@
       </c>
       <c r="DW1" t="inlineStr">
         <is>
+          <t>pinnacle_ft_over25</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>pinnacle_ft_over15</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>pinnacle_ft_over35</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>pinnacle_1st_half_over15</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>pinnacle_1st_half_under15</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>pinnacle_1st_half_over05</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>pinnacle_1st_half_under05</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
           <t>pinnacle_corners_over_95</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>pinnacle_corners_under_95</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>pinnacle_corners_over_85</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>pinnacle_corners_under_85</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>pinnacle_1st_half_over15</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>pinnacle_1st_half_under15</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>pinnacle_1st_half_under05</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>pinnacle_1st_half_over05</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>pinnacle_ft_over25</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>pinnacle_ft_over35</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>pinnacle_ft_over15</t>
-        </is>
-      </c>
       <c r="EH1" t="inlineStr">
         <is>
           <t>pinnacle_ft_x</t>
@@ -1404,12 +1404,12 @@
       </c>
       <c r="EI1" t="inlineStr">
         <is>
+          <t>pinnacle_ft_1</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
           <t>pinnacle_ft_2</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>pinnacle_ft_1</t>
         </is>
       </c>
     </row>
@@ -1796,37 +1796,37 @@
       <c r="DV2" t="b">
         <v>0</v>
       </c>
-      <c r="DW2" t="inlineStr"/>
-      <c r="DX2" t="inlineStr"/>
-      <c r="DY2" t="inlineStr"/>
-      <c r="DZ2" t="inlineStr"/>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
       <c r="EA2" t="inlineStr">
         <is>
-          <t>2.46</t>
-        </is>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
           <t>1.57</t>
         </is>
       </c>
+      <c r="EB2" t="inlineStr"/>
       <c r="EC2" t="inlineStr"/>
       <c r="ED2" t="inlineStr"/>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>1.20</t>
-        </is>
-      </c>
+      <c r="EE2" t="inlineStr"/>
+      <c r="EF2" t="inlineStr"/>
+      <c r="EG2" t="inlineStr"/>
       <c r="EH2" t="inlineStr">
         <is>
           <t>4.90</t>
@@ -1834,12 +1834,12 @@
       </c>
       <c r="EI2" t="inlineStr">
         <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EJ2" t="inlineStr">
+        <is>
           <t>7.56</t>
-        </is>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>1.41</t>
         </is>
       </c>
     </row>
@@ -2226,37 +2226,37 @@
       <c r="DV3" t="b">
         <v>0</v>
       </c>
-      <c r="DW3" t="inlineStr"/>
-      <c r="DX3" t="inlineStr"/>
-      <c r="DY3" t="inlineStr"/>
-      <c r="DZ3" t="inlineStr"/>
+      <c r="DW3" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="DX3" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="DY3" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="DZ3" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
       <c r="EA3" t="inlineStr">
         <is>
-          <t>2.21</t>
-        </is>
-      </c>
-      <c r="EB3" t="inlineStr">
-        <is>
           <t>1.69</t>
         </is>
       </c>
+      <c r="EB3" t="inlineStr"/>
       <c r="EC3" t="inlineStr"/>
       <c r="ED3" t="inlineStr"/>
-      <c r="EE3" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="EF3" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="EG3" t="inlineStr">
-        <is>
-          <t>1.15</t>
-        </is>
-      </c>
+      <c r="EE3" t="inlineStr"/>
+      <c r="EF3" t="inlineStr"/>
+      <c r="EG3" t="inlineStr"/>
       <c r="EH3" t="inlineStr">
         <is>
           <t>4.51</t>
@@ -2264,12 +2264,12 @@
       </c>
       <c r="EI3" t="inlineStr">
         <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="EJ3" t="inlineStr">
+        <is>
           <t>5.15</t>
-        </is>
-      </c>
-      <c r="EJ3" t="inlineStr">
-        <is>
-          <t>1.59</t>
         </is>
       </c>
     </row>
@@ -2658,51 +2658,51 @@
       </c>
       <c r="DW4" t="inlineStr">
         <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="DX4" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="DY4" t="inlineStr">
+        <is>
+          <t>2.61</t>
+        </is>
+      </c>
+      <c r="DZ4" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="EA4" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EB4" t="inlineStr"/>
+      <c r="EC4" t="inlineStr"/>
+      <c r="ED4" t="inlineStr">
+        <is>
           <t>1.75</t>
         </is>
       </c>
-      <c r="DX4" t="inlineStr">
+      <c r="EE4" t="inlineStr">
         <is>
           <t>2.04</t>
         </is>
       </c>
-      <c r="DY4" t="inlineStr">
+      <c r="EF4" t="inlineStr">
         <is>
           <t>1.45</t>
         </is>
       </c>
-      <c r="DZ4" t="inlineStr">
+      <c r="EG4" t="inlineStr">
         <is>
           <t>2.59</t>
         </is>
       </c>
-      <c r="EA4" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="EB4" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="EC4" t="inlineStr"/>
-      <c r="ED4" t="inlineStr"/>
-      <c r="EE4" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="EF4" t="inlineStr">
-        <is>
-          <t>2.61</t>
-        </is>
-      </c>
-      <c r="EG4" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
       <c r="EH4" t="inlineStr">
         <is>
           <t>3.91</t>
@@ -2710,12 +2710,12 @@
       </c>
       <c r="EI4" t="inlineStr">
         <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EJ4" t="inlineStr">
+        <is>
           <t>4.15</t>
-        </is>
-      </c>
-      <c r="EJ4" t="inlineStr">
-        <is>
-          <t>1.83</t>
         </is>
       </c>
     </row>
@@ -3102,37 +3102,37 @@
       <c r="DV5" t="b">
         <v>1</v>
       </c>
-      <c r="DW5" t="inlineStr"/>
-      <c r="DX5" t="inlineStr"/>
-      <c r="DY5" t="inlineStr"/>
-      <c r="DZ5" t="inlineStr"/>
+      <c r="DW5" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="DX5" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="DY5" t="inlineStr">
+        <is>
+          <t>2.59</t>
+        </is>
+      </c>
+      <c r="DZ5" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
       <c r="EA5" t="inlineStr">
         <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="EB5" t="inlineStr">
-        <is>
           <t>1.55</t>
         </is>
       </c>
+      <c r="EB5" t="inlineStr"/>
       <c r="EC5" t="inlineStr"/>
       <c r="ED5" t="inlineStr"/>
-      <c r="EE5" t="inlineStr">
-        <is>
-          <t>1.68</t>
-        </is>
-      </c>
-      <c r="EF5" t="inlineStr">
-        <is>
-          <t>2.59</t>
-        </is>
-      </c>
-      <c r="EG5" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
-      </c>
+      <c r="EE5" t="inlineStr"/>
+      <c r="EF5" t="inlineStr"/>
+      <c r="EG5" t="inlineStr"/>
       <c r="EH5" t="inlineStr">
         <is>
           <t>3.37</t>
@@ -3140,12 +3140,12 @@
       </c>
       <c r="EI5" t="inlineStr">
         <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="EJ5" t="inlineStr">
+        <is>
           <t>3.71</t>
-        </is>
-      </c>
-      <c r="EJ5" t="inlineStr">
-        <is>
-          <t>2.11</t>
         </is>
       </c>
     </row>
@@ -3532,29 +3532,29 @@
       <c r="DV6" t="b">
         <v>0</v>
       </c>
-      <c r="DW6" t="inlineStr"/>
-      <c r="DX6" t="inlineStr"/>
-      <c r="DY6" t="inlineStr"/>
+      <c r="DW6" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="DX6" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="DY6" t="inlineStr">
+        <is>
+          <t>2.79</t>
+        </is>
+      </c>
       <c r="DZ6" t="inlineStr"/>
       <c r="EA6" t="inlineStr"/>
       <c r="EB6" t="inlineStr"/>
       <c r="EC6" t="inlineStr"/>
       <c r="ED6" t="inlineStr"/>
-      <c r="EE6" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="EF6" t="inlineStr">
-        <is>
-          <t>2.79</t>
-        </is>
-      </c>
-      <c r="EG6" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
-      </c>
+      <c r="EE6" t="inlineStr"/>
+      <c r="EF6" t="inlineStr"/>
+      <c r="EG6" t="inlineStr"/>
       <c r="EH6" t="inlineStr">
         <is>
           <t>3.57</t>
@@ -3562,12 +3562,12 @@
       </c>
       <c r="EI6" t="inlineStr">
         <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="EJ6" t="inlineStr">
+        <is>
           <t>2.47</t>
-        </is>
-      </c>
-      <c r="EJ6" t="inlineStr">
-        <is>
-          <t>2.83</t>
         </is>
       </c>
     </row>
@@ -3956,43 +3956,43 @@
       </c>
       <c r="DW7" t="inlineStr">
         <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="DX7" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="DY7" t="inlineStr">
+        <is>
+          <t>2.67</t>
+        </is>
+      </c>
+      <c r="DZ7" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="EA7" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EB7" t="inlineStr"/>
+      <c r="EC7" t="inlineStr"/>
+      <c r="ED7" t="inlineStr">
+        <is>
           <t>1.59</t>
         </is>
       </c>
-      <c r="DX7" t="inlineStr">
+      <c r="EE7" t="inlineStr">
         <is>
           <t>2.26</t>
         </is>
       </c>
-      <c r="DY7" t="inlineStr"/>
-      <c r="DZ7" t="inlineStr"/>
-      <c r="EA7" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="EB7" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="EC7" t="inlineStr"/>
-      <c r="ED7" t="inlineStr"/>
-      <c r="EE7" t="inlineStr">
-        <is>
-          <t>1.69</t>
-        </is>
-      </c>
-      <c r="EF7" t="inlineStr">
-        <is>
-          <t>2.67</t>
-        </is>
-      </c>
-      <c r="EG7" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
+      <c r="EF7" t="inlineStr"/>
+      <c r="EG7" t="inlineStr"/>
       <c r="EH7" t="inlineStr">
         <is>
           <t>3.59</t>
@@ -4000,12 +4000,12 @@
       </c>
       <c r="EI7" t="inlineStr">
         <is>
+          <t>2.94</t>
+        </is>
+      </c>
+      <c r="EJ7" t="inlineStr">
+        <is>
           <t>2.38</t>
-        </is>
-      </c>
-      <c r="EJ7" t="inlineStr">
-        <is>
-          <t>2.94</t>
         </is>
       </c>
     </row>
@@ -4394,72 +4394,72 @@
       </c>
       <c r="DW8" t="inlineStr">
         <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="DX8" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="DY8" t="inlineStr">
+        <is>
+          <t>3.07</t>
+        </is>
+      </c>
+      <c r="DZ8" t="inlineStr">
+        <is>
+          <t>2.81</t>
+        </is>
+      </c>
+      <c r="EA8" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EB8" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EC8" t="inlineStr">
+        <is>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="ED8" t="inlineStr">
+        <is>
           <t>1.99</t>
         </is>
       </c>
-      <c r="DX8" t="inlineStr">
+      <c r="EE8" t="inlineStr">
         <is>
           <t>1.83</t>
         </is>
       </c>
-      <c r="DY8" t="inlineStr">
+      <c r="EF8" t="inlineStr">
         <is>
           <t>1.56</t>
         </is>
       </c>
-      <c r="DZ8" t="inlineStr">
+      <c r="EG8" t="inlineStr">
         <is>
           <t>2.32</t>
         </is>
       </c>
-      <c r="EA8" t="inlineStr">
-        <is>
-          <t>2.81</t>
-        </is>
-      </c>
-      <c r="EB8" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="EC8" t="inlineStr">
+      <c r="EH8" t="inlineStr">
+        <is>
+          <t>3.67</t>
+        </is>
+      </c>
+      <c r="EI8" t="inlineStr">
         <is>
           <t>3.19</t>
         </is>
       </c>
-      <c r="ED8" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="EE8" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="EF8" t="inlineStr">
-        <is>
-          <t>3.07</t>
-        </is>
-      </c>
-      <c r="EG8" t="inlineStr">
-        <is>
-          <t>1.26</t>
-        </is>
-      </c>
-      <c r="EH8" t="inlineStr">
-        <is>
-          <t>3.67</t>
-        </is>
-      </c>
-      <c r="EI8" t="inlineStr">
+      <c r="EJ8" t="inlineStr">
         <is>
           <t>2.24</t>
-        </is>
-      </c>
-      <c r="EJ8" t="inlineStr">
-        <is>
-          <t>3.19</t>
         </is>
       </c>
     </row>
@@ -4846,18 +4846,34 @@
       <c r="DV9" t="b">
         <v>0</v>
       </c>
-      <c r="DW9" t="inlineStr"/>
-      <c r="DX9" t="inlineStr"/>
-      <c r="DY9" t="inlineStr"/>
-      <c r="DZ9" t="inlineStr"/>
+      <c r="DW9" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="DX9" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="DY9" t="inlineStr">
+        <is>
+          <t>2.81</t>
+        </is>
+      </c>
+      <c r="DZ9" t="inlineStr">
+        <is>
+          <t>2.61</t>
+        </is>
+      </c>
       <c r="EA9" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EB9" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EC9" t="inlineStr">
@@ -4865,26 +4881,10 @@
           <t>3.37</t>
         </is>
       </c>
-      <c r="ED9" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="EE9" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="EF9" t="inlineStr">
-        <is>
-          <t>2.81</t>
-        </is>
-      </c>
-      <c r="EG9" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
+      <c r="ED9" t="inlineStr"/>
+      <c r="EE9" t="inlineStr"/>
+      <c r="EF9" t="inlineStr"/>
+      <c r="EG9" t="inlineStr"/>
       <c r="EH9" t="inlineStr">
         <is>
           <t>4.00</t>
@@ -4892,12 +4892,12 @@
       </c>
       <c r="EI9" t="inlineStr">
         <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EJ9" t="inlineStr">
+        <is>
           <t>5.59</t>
-        </is>
-      </c>
-      <c r="EJ9" t="inlineStr">
-        <is>
-          <t>1.65</t>
         </is>
       </c>
     </row>
@@ -5286,51 +5286,51 @@
       </c>
       <c r="DW10" t="inlineStr">
         <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="DX10" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="DY10" t="inlineStr">
+        <is>
+          <t>3.27</t>
+        </is>
+      </c>
+      <c r="DZ10" t="inlineStr">
+        <is>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="EA10" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EB10" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EC10" t="inlineStr">
+        <is>
+          <t>3.08</t>
+        </is>
+      </c>
+      <c r="ED10" t="inlineStr">
+        <is>
           <t>1.74</t>
         </is>
       </c>
-      <c r="DX10" t="inlineStr">
+      <c r="EE10" t="inlineStr">
         <is>
           <t>2.07</t>
         </is>
       </c>
-      <c r="DY10" t="inlineStr"/>
-      <c r="DZ10" t="inlineStr"/>
-      <c r="EA10" t="inlineStr">
-        <is>
-          <t>2.93</t>
-        </is>
-      </c>
-      <c r="EB10" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="EC10" t="inlineStr">
-        <is>
-          <t>3.08</t>
-        </is>
-      </c>
-      <c r="ED10" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EE10" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
-      <c r="EF10" t="inlineStr">
-        <is>
-          <t>3.27</t>
-        </is>
-      </c>
-      <c r="EG10" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
+      <c r="EF10" t="inlineStr"/>
+      <c r="EG10" t="inlineStr"/>
       <c r="EH10" t="inlineStr">
         <is>
           <t>3.67</t>
@@ -5338,12 +5338,12 @@
       </c>
       <c r="EI10" t="inlineStr">
         <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EJ10" t="inlineStr">
+        <is>
           <t>3.71</t>
-        </is>
-      </c>
-      <c r="EJ10" t="inlineStr">
-        <is>
-          <t>2.03</t>
         </is>
       </c>
     </row>
@@ -5732,43 +5732,43 @@
       </c>
       <c r="DW11" t="inlineStr">
         <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="DX11" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="DY11" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="DZ11" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EA11" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EB11" t="inlineStr"/>
+      <c r="EC11" t="inlineStr"/>
+      <c r="ED11" t="inlineStr">
+        <is>
           <t>1.64</t>
         </is>
       </c>
-      <c r="DX11" t="inlineStr">
+      <c r="EE11" t="inlineStr">
         <is>
           <t>2.22</t>
         </is>
       </c>
-      <c r="DY11" t="inlineStr"/>
-      <c r="DZ11" t="inlineStr"/>
-      <c r="EA11" t="inlineStr">
-        <is>
-          <t>2.18</t>
-        </is>
-      </c>
-      <c r="EB11" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="EC11" t="inlineStr"/>
-      <c r="ED11" t="inlineStr"/>
-      <c r="EE11" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="EF11" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="EG11" t="inlineStr">
-        <is>
-          <t>1.15</t>
-        </is>
-      </c>
+      <c r="EF11" t="inlineStr"/>
+      <c r="EG11" t="inlineStr"/>
       <c r="EH11" t="inlineStr">
         <is>
           <t>5.25</t>
@@ -5776,12 +5776,12 @@
       </c>
       <c r="EI11" t="inlineStr">
         <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EJ11" t="inlineStr">
+        <is>
           <t>7.24</t>
-        </is>
-      </c>
-      <c r="EJ11" t="inlineStr">
-        <is>
-          <t>1.41</t>
         </is>
       </c>
     </row>
@@ -6170,43 +6170,43 @@
       </c>
       <c r="DW12" t="inlineStr">
         <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="DX12" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="DY12" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="DZ12" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EA12" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EB12" t="inlineStr"/>
+      <c r="EC12" t="inlineStr"/>
+      <c r="ED12" t="inlineStr">
+        <is>
           <t>1.65</t>
         </is>
       </c>
-      <c r="DX12" t="inlineStr">
+      <c r="EE12" t="inlineStr">
         <is>
           <t>2.18</t>
         </is>
       </c>
-      <c r="DY12" t="inlineStr"/>
-      <c r="DZ12" t="inlineStr"/>
-      <c r="EA12" t="inlineStr">
-        <is>
-          <t>2.22</t>
-        </is>
-      </c>
-      <c r="EB12" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="EC12" t="inlineStr"/>
-      <c r="ED12" t="inlineStr"/>
-      <c r="EE12" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="EF12" t="inlineStr">
-        <is>
-          <t>2.19</t>
-        </is>
-      </c>
-      <c r="EG12" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
+      <c r="EF12" t="inlineStr"/>
+      <c r="EG12" t="inlineStr"/>
       <c r="EH12" t="inlineStr">
         <is>
           <t>4.41</t>
@@ -6214,12 +6214,12 @@
       </c>
       <c r="EI12" t="inlineStr">
         <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EJ12" t="inlineStr">
+        <is>
           <t>4.64</t>
-        </is>
-      </c>
-      <c r="EJ12" t="inlineStr">
-        <is>
-          <t>1.68</t>
         </is>
       </c>
     </row>
@@ -6606,18 +6606,34 @@
       <c r="DV13" t="b">
         <v>1</v>
       </c>
-      <c r="DW13" t="inlineStr"/>
-      <c r="DX13" t="inlineStr"/>
-      <c r="DY13" t="inlineStr"/>
-      <c r="DZ13" t="inlineStr"/>
+      <c r="DW13" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="DX13" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="DY13" t="inlineStr">
+        <is>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="DZ13" t="inlineStr">
+        <is>
+          <t>2.67</t>
+        </is>
+      </c>
       <c r="EA13" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EB13" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EC13" t="inlineStr">
@@ -6625,26 +6641,10 @@
           <t>3.38</t>
         </is>
       </c>
-      <c r="ED13" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="EE13" t="inlineStr">
-        <is>
-          <t>1.79</t>
-        </is>
-      </c>
-      <c r="EF13" t="inlineStr">
-        <is>
-          <t>2.93</t>
-        </is>
-      </c>
-      <c r="EG13" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
+      <c r="ED13" t="inlineStr"/>
+      <c r="EE13" t="inlineStr"/>
+      <c r="EF13" t="inlineStr"/>
+      <c r="EG13" t="inlineStr"/>
       <c r="EH13" t="inlineStr">
         <is>
           <t>3.44</t>
@@ -6652,12 +6652,12 @@
       </c>
       <c r="EI13" t="inlineStr">
         <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="EJ13" t="inlineStr">
+        <is>
           <t>3.38</t>
-        </is>
-      </c>
-      <c r="EJ13" t="inlineStr">
-        <is>
-          <t>2.24</t>
         </is>
       </c>
     </row>
@@ -7046,43 +7046,43 @@
       </c>
       <c r="DW14" t="inlineStr">
         <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="DX14" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="DY14" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="DZ14" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EA14" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EB14" t="inlineStr"/>
+      <c r="EC14" t="inlineStr"/>
+      <c r="ED14" t="inlineStr">
+        <is>
           <t>1.50</t>
         </is>
       </c>
-      <c r="DX14" t="inlineStr">
+      <c r="EE14" t="inlineStr">
         <is>
           <t>2.46</t>
         </is>
       </c>
-      <c r="DY14" t="inlineStr"/>
-      <c r="DZ14" t="inlineStr"/>
-      <c r="EA14" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="EB14" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="EC14" t="inlineStr"/>
-      <c r="ED14" t="inlineStr"/>
-      <c r="EE14" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="EF14" t="inlineStr">
-        <is>
-          <t>2.16</t>
-        </is>
-      </c>
-      <c r="EG14" t="inlineStr">
-        <is>
-          <t>1.15</t>
-        </is>
-      </c>
+      <c r="EF14" t="inlineStr"/>
+      <c r="EG14" t="inlineStr"/>
       <c r="EH14" t="inlineStr">
         <is>
           <t>4.45</t>
@@ -7090,12 +7090,12 @@
       </c>
       <c r="EI14" t="inlineStr">
         <is>
+          <t>4.66</t>
+        </is>
+      </c>
+      <c r="EJ14" t="inlineStr">
+        <is>
           <t>1.67</t>
-        </is>
-      </c>
-      <c r="EJ14" t="inlineStr">
-        <is>
-          <t>4.66</t>
         </is>
       </c>
     </row>
@@ -7482,37 +7482,37 @@
       <c r="DV15" t="b">
         <v>1</v>
       </c>
-      <c r="DW15" t="inlineStr"/>
-      <c r="DX15" t="inlineStr"/>
-      <c r="DY15" t="inlineStr"/>
-      <c r="DZ15" t="inlineStr"/>
+      <c r="DW15" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="DX15" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="DY15" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="DZ15" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
       <c r="EA15" t="inlineStr">
         <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="EB15" t="inlineStr">
-        <is>
           <t>1.56</t>
         </is>
       </c>
+      <c r="EB15" t="inlineStr"/>
       <c r="EC15" t="inlineStr"/>
       <c r="ED15" t="inlineStr"/>
-      <c r="EE15" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="EF15" t="inlineStr">
-        <is>
-          <t>2.64</t>
-        </is>
-      </c>
-      <c r="EG15" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
+      <c r="EE15" t="inlineStr"/>
+      <c r="EF15" t="inlineStr"/>
+      <c r="EG15" t="inlineStr"/>
       <c r="EH15" t="inlineStr">
         <is>
           <t>4.39</t>
@@ -7520,12 +7520,12 @@
       </c>
       <c r="EI15" t="inlineStr">
         <is>
+          <t>5.49</t>
+        </is>
+      </c>
+      <c r="EJ15" t="inlineStr">
+        <is>
           <t>1.59</t>
-        </is>
-      </c>
-      <c r="EJ15" t="inlineStr">
-        <is>
-          <t>5.49</t>
         </is>
       </c>
     </row>
@@ -7914,59 +7914,59 @@
       </c>
       <c r="DW16" t="inlineStr">
         <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="DX16" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="DY16" t="inlineStr">
+        <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="DZ16" t="inlineStr">
+        <is>
+          <t>2.82</t>
+        </is>
+      </c>
+      <c r="EA16" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EB16" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EC16" t="inlineStr">
+        <is>
+          <t>3.21</t>
+        </is>
+      </c>
+      <c r="ED16" t="inlineStr">
+        <is>
           <t>1.85</t>
         </is>
       </c>
-      <c r="DX16" t="inlineStr">
+      <c r="EE16" t="inlineStr">
         <is>
           <t>1.96</t>
         </is>
       </c>
-      <c r="DY16" t="inlineStr">
+      <c r="EF16" t="inlineStr">
         <is>
           <t>1.48</t>
         </is>
       </c>
-      <c r="DZ16" t="inlineStr">
+      <c r="EG16" t="inlineStr">
         <is>
           <t>2.53</t>
         </is>
       </c>
-      <c r="EA16" t="inlineStr">
-        <is>
-          <t>2.82</t>
-        </is>
-      </c>
-      <c r="EB16" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="EC16" t="inlineStr">
-        <is>
-          <t>3.21</t>
-        </is>
-      </c>
-      <c r="ED16" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="EE16" t="inlineStr">
-        <is>
-          <t>1.89</t>
-        </is>
-      </c>
-      <c r="EF16" t="inlineStr">
-        <is>
-          <t>3.18</t>
-        </is>
-      </c>
-      <c r="EG16" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
       <c r="EH16" t="inlineStr">
         <is>
           <t>3.96</t>
@@ -7974,12 +7974,12 @@
       </c>
       <c r="EI16" t="inlineStr">
         <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="EJ16" t="inlineStr">
+        <is>
           <t>5.35</t>
-        </is>
-      </c>
-      <c r="EJ16" t="inlineStr">
-        <is>
-          <t>1.67</t>
         </is>
       </c>
     </row>
@@ -8366,37 +8366,37 @@
       <c r="DV17" t="b">
         <v>0</v>
       </c>
-      <c r="DW17" t="inlineStr"/>
-      <c r="DX17" t="inlineStr"/>
-      <c r="DY17" t="inlineStr"/>
-      <c r="DZ17" t="inlineStr"/>
+      <c r="DW17" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="DX17" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="DY17" t="inlineStr">
+        <is>
+          <t>2.61</t>
+        </is>
+      </c>
+      <c r="DZ17" t="inlineStr">
+        <is>
+          <t>2.47</t>
+        </is>
+      </c>
       <c r="EA17" t="inlineStr">
         <is>
-          <t>2.47</t>
-        </is>
-      </c>
-      <c r="EB17" t="inlineStr">
-        <is>
           <t>1.58</t>
         </is>
       </c>
+      <c r="EB17" t="inlineStr"/>
       <c r="EC17" t="inlineStr"/>
       <c r="ED17" t="inlineStr"/>
-      <c r="EE17" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="EF17" t="inlineStr">
-        <is>
-          <t>2.61</t>
-        </is>
-      </c>
-      <c r="EG17" t="inlineStr">
-        <is>
-          <t>1.20</t>
-        </is>
-      </c>
+      <c r="EE17" t="inlineStr"/>
+      <c r="EF17" t="inlineStr"/>
+      <c r="EG17" t="inlineStr"/>
       <c r="EH17" t="inlineStr">
         <is>
           <t>3.86</t>
@@ -8404,12 +8404,12 @@
       </c>
       <c r="EI17" t="inlineStr">
         <is>
+          <t>3.66</t>
+        </is>
+      </c>
+      <c r="EJ17" t="inlineStr">
+        <is>
           <t>1.99</t>
-        </is>
-      </c>
-      <c r="EJ17" t="inlineStr">
-        <is>
-          <t>3.66</t>
         </is>
       </c>
     </row>
@@ -8798,59 +8798,59 @@
       </c>
       <c r="DW18" t="inlineStr">
         <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="DX18" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="DY18" t="inlineStr">
+        <is>
+          <t>4.01</t>
+        </is>
+      </c>
+      <c r="DZ18" t="inlineStr">
+        <is>
+          <t>3.26</t>
+        </is>
+      </c>
+      <c r="EA18" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EB18" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EC18" t="inlineStr">
+        <is>
+          <t>2.82</t>
+        </is>
+      </c>
+      <c r="ED18" t="inlineStr">
+        <is>
           <t>1.97</t>
         </is>
       </c>
-      <c r="DX18" t="inlineStr">
+      <c r="EE18" t="inlineStr">
         <is>
           <t>1.85</t>
         </is>
       </c>
-      <c r="DY18" t="inlineStr">
+      <c r="EF18" t="inlineStr">
         <is>
           <t>1.58</t>
         </is>
       </c>
-      <c r="DZ18" t="inlineStr">
+      <c r="EG18" t="inlineStr">
         <is>
           <t>2.31</t>
         </is>
       </c>
-      <c r="EA18" t="inlineStr">
-        <is>
-          <t>3.26</t>
-        </is>
-      </c>
-      <c r="EB18" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="EC18" t="inlineStr">
-        <is>
-          <t>2.82</t>
-        </is>
-      </c>
-      <c r="ED18" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="EE18" t="inlineStr">
-        <is>
-          <t>2.19</t>
-        </is>
-      </c>
-      <c r="EF18" t="inlineStr">
-        <is>
-          <t>4.01</t>
-        </is>
-      </c>
-      <c r="EG18" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
       <c r="EH18" t="inlineStr">
         <is>
           <t>3.54</t>
@@ -8858,12 +8858,12 @@
       </c>
       <c r="EI18" t="inlineStr">
         <is>
+          <t>3.93</t>
+        </is>
+      </c>
+      <c r="EJ18" t="inlineStr">
+        <is>
           <t>2.01</t>
-        </is>
-      </c>
-      <c r="EJ18" t="inlineStr">
-        <is>
-          <t>3.93</t>
         </is>
       </c>
     </row>
@@ -9250,37 +9250,37 @@
       <c r="DV19" t="b">
         <v>1</v>
       </c>
-      <c r="DW19" t="inlineStr"/>
-      <c r="DX19" t="inlineStr"/>
-      <c r="DY19" t="inlineStr"/>
-      <c r="DZ19" t="inlineStr"/>
+      <c r="DW19" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="DX19" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="DY19" t="inlineStr">
+        <is>
+          <t>2.59</t>
+        </is>
+      </c>
+      <c r="DZ19" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
       <c r="EA19" t="inlineStr">
         <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="EB19" t="inlineStr">
-        <is>
           <t>1.56</t>
         </is>
       </c>
+      <c r="EB19" t="inlineStr"/>
       <c r="EC19" t="inlineStr"/>
       <c r="ED19" t="inlineStr"/>
-      <c r="EE19" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
-      <c r="EF19" t="inlineStr">
-        <is>
-          <t>2.59</t>
-        </is>
-      </c>
-      <c r="EG19" t="inlineStr">
-        <is>
-          <t>1.20</t>
-        </is>
-      </c>
+      <c r="EE19" t="inlineStr"/>
+      <c r="EF19" t="inlineStr"/>
+      <c r="EG19" t="inlineStr"/>
       <c r="EH19" t="inlineStr">
         <is>
           <t>4.91</t>
@@ -9288,12 +9288,12 @@
       </c>
       <c r="EI19" t="inlineStr">
         <is>
+          <t>5.95</t>
+        </is>
+      </c>
+      <c r="EJ19" t="inlineStr">
+        <is>
           <t>1.50</t>
-        </is>
-      </c>
-      <c r="EJ19" t="inlineStr">
-        <is>
-          <t>5.95</t>
         </is>
       </c>
     </row>
@@ -9680,18 +9680,34 @@
       <c r="DV20" t="b">
         <v>1</v>
       </c>
-      <c r="DW20" t="inlineStr"/>
-      <c r="DX20" t="inlineStr"/>
-      <c r="DY20" t="inlineStr"/>
-      <c r="DZ20" t="inlineStr"/>
+      <c r="DW20" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="DX20" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="DY20" t="inlineStr">
+        <is>
+          <t>2.87</t>
+        </is>
+      </c>
+      <c r="DZ20" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
       <c r="EA20" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="EB20" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="EC20" t="inlineStr">
@@ -9699,26 +9715,10 @@
           <t>3.34</t>
         </is>
       </c>
-      <c r="ED20" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
-      <c r="EE20" t="inlineStr">
-        <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="EF20" t="inlineStr">
-        <is>
-          <t>2.87</t>
-        </is>
-      </c>
-      <c r="EG20" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
+      <c r="ED20" t="inlineStr"/>
+      <c r="EE20" t="inlineStr"/>
+      <c r="EF20" t="inlineStr"/>
+      <c r="EG20" t="inlineStr"/>
       <c r="EH20" t="inlineStr">
         <is>
           <t>3.85</t>
@@ -9726,12 +9726,12 @@
       </c>
       <c r="EI20" t="inlineStr">
         <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EJ20" t="inlineStr">
+        <is>
           <t>4.11</t>
-        </is>
-      </c>
-      <c r="EJ20" t="inlineStr">
-        <is>
-          <t>1.88</t>
         </is>
       </c>
     </row>
@@ -10120,43 +10120,43 @@
       </c>
       <c r="DW21" t="inlineStr">
         <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="DX21" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="DY21" t="inlineStr">
+        <is>
+          <t>2.68</t>
+        </is>
+      </c>
+      <c r="DZ21" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="EA21" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="EB21" t="inlineStr"/>
+      <c r="EC21" t="inlineStr"/>
+      <c r="ED21" t="inlineStr">
+        <is>
           <t>1.59</t>
         </is>
       </c>
-      <c r="DX21" t="inlineStr">
+      <c r="EE21" t="inlineStr">
         <is>
           <t>2.26</t>
         </is>
       </c>
-      <c r="DY21" t="inlineStr"/>
-      <c r="DZ21" t="inlineStr"/>
-      <c r="EA21" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="EB21" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
-      <c r="EC21" t="inlineStr"/>
-      <c r="ED21" t="inlineStr"/>
-      <c r="EE21" t="inlineStr">
-        <is>
-          <t>1.69</t>
-        </is>
-      </c>
-      <c r="EF21" t="inlineStr">
-        <is>
-          <t>2.68</t>
-        </is>
-      </c>
-      <c r="EG21" t="inlineStr">
-        <is>
-          <t>1.20</t>
-        </is>
-      </c>
+      <c r="EF21" t="inlineStr"/>
+      <c r="EG21" t="inlineStr"/>
       <c r="EH21" t="inlineStr">
         <is>
           <t>3.68</t>
@@ -10164,12 +10164,12 @@
       </c>
       <c r="EI21" t="inlineStr">
         <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="EJ21" t="inlineStr">
+        <is>
           <t>3.05</t>
-        </is>
-      </c>
-      <c r="EJ21" t="inlineStr">
-        <is>
-          <t>2.30</t>
         </is>
       </c>
     </row>
@@ -10556,18 +10556,34 @@
       <c r="DV22" t="b">
         <v>1</v>
       </c>
-      <c r="DW22" t="inlineStr"/>
-      <c r="DX22" t="inlineStr"/>
-      <c r="DY22" t="inlineStr"/>
-      <c r="DZ22" t="inlineStr"/>
+      <c r="DW22" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="DX22" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="DY22" t="inlineStr">
+        <is>
+          <t>2.82</t>
+        </is>
+      </c>
+      <c r="DZ22" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
       <c r="EA22" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="EB22" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="EC22" t="inlineStr">
@@ -10575,26 +10591,10 @@
           <t>3.32</t>
         </is>
       </c>
-      <c r="ED22" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
-      <c r="EE22" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="EF22" t="inlineStr">
-        <is>
-          <t>2.82</t>
-        </is>
-      </c>
-      <c r="EG22" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
+      <c r="ED22" t="inlineStr"/>
+      <c r="EE22" t="inlineStr"/>
+      <c r="EF22" t="inlineStr"/>
+      <c r="EG22" t="inlineStr"/>
       <c r="EH22" t="inlineStr">
         <is>
           <t>3.70</t>
@@ -10602,12 +10602,12 @@
       </c>
       <c r="EI22" t="inlineStr">
         <is>
+          <t>3.49</t>
+        </is>
+      </c>
+      <c r="EJ22" t="inlineStr">
+        <is>
           <t>2.10</t>
-        </is>
-      </c>
-      <c r="EJ22" t="inlineStr">
-        <is>
-          <t>3.49</t>
         </is>
       </c>
     </row>
@@ -10996,51 +10996,51 @@
       </c>
       <c r="DW23" t="inlineStr">
         <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="DX23" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="DY23" t="inlineStr">
+        <is>
+          <t>2.61</t>
+        </is>
+      </c>
+      <c r="DZ23" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="EA23" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EB23" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EC23" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="ED23" t="inlineStr">
+        <is>
           <t>1.76</t>
         </is>
       </c>
-      <c r="DX23" t="inlineStr">
+      <c r="EE23" t="inlineStr">
         <is>
           <t>2.02</t>
         </is>
       </c>
-      <c r="DY23" t="inlineStr"/>
-      <c r="DZ23" t="inlineStr"/>
-      <c r="EA23" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="EB23" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="EC23" t="inlineStr">
-        <is>
-          <t>3.34</t>
-        </is>
-      </c>
-      <c r="ED23" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
-      <c r="EE23" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="EF23" t="inlineStr">
-        <is>
-          <t>2.61</t>
-        </is>
-      </c>
-      <c r="EG23" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
+      <c r="EF23" t="inlineStr"/>
+      <c r="EG23" t="inlineStr"/>
       <c r="EH23" t="inlineStr">
         <is>
           <t>3.83</t>
@@ -11048,12 +11048,12 @@
       </c>
       <c r="EI23" t="inlineStr">
         <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EJ23" t="inlineStr">
+        <is>
           <t>3.70</t>
-        </is>
-      </c>
-      <c r="EJ23" t="inlineStr">
-        <is>
-          <t>1.99</t>
         </is>
       </c>
     </row>
@@ -11440,18 +11440,34 @@
       <c r="DV24" t="b">
         <v>1</v>
       </c>
-      <c r="DW24" t="inlineStr"/>
-      <c r="DX24" t="inlineStr"/>
-      <c r="DY24" t="inlineStr"/>
-      <c r="DZ24" t="inlineStr"/>
+      <c r="DW24" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="DX24" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="DY24" t="inlineStr">
+        <is>
+          <t>3.73</t>
+        </is>
+      </c>
+      <c r="DZ24" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
       <c r="EA24" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="EB24" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="EC24" t="inlineStr">
@@ -11459,26 +11475,10 @@
           <t>2.98</t>
         </is>
       </c>
-      <c r="ED24" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="EE24" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="EF24" t="inlineStr">
-        <is>
-          <t>3.73</t>
-        </is>
-      </c>
-      <c r="EG24" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
+      <c r="ED24" t="inlineStr"/>
+      <c r="EE24" t="inlineStr"/>
+      <c r="EF24" t="inlineStr"/>
+      <c r="EG24" t="inlineStr"/>
       <c r="EH24" t="inlineStr">
         <is>
           <t>3.48</t>
@@ -11486,12 +11486,12 @@
       </c>
       <c r="EI24" t="inlineStr">
         <is>
+          <t>2.92</t>
+        </is>
+      </c>
+      <c r="EJ24" t="inlineStr">
+        <is>
           <t>2.48</t>
-        </is>
-      </c>
-      <c r="EJ24" t="inlineStr">
-        <is>
-          <t>2.92</t>
         </is>
       </c>
     </row>
@@ -11880,43 +11880,43 @@
       </c>
       <c r="DW25" t="inlineStr">
         <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="DX25" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="DY25" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="DZ25" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EA25" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EB25" t="inlineStr"/>
+      <c r="EC25" t="inlineStr"/>
+      <c r="ED25" t="inlineStr">
+        <is>
           <t>1.70</t>
         </is>
       </c>
-      <c r="DX25" t="inlineStr">
+      <c r="EE25" t="inlineStr">
         <is>
           <t>2.10</t>
         </is>
       </c>
-      <c r="DY25" t="inlineStr"/>
-      <c r="DZ25" t="inlineStr"/>
-      <c r="EA25" t="inlineStr">
-        <is>
-          <t>2.52</t>
-        </is>
-      </c>
-      <c r="EB25" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="EC25" t="inlineStr"/>
-      <c r="ED25" t="inlineStr"/>
-      <c r="EE25" t="inlineStr">
-        <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="EF25" t="inlineStr">
-        <is>
-          <t>2.64</t>
-        </is>
-      </c>
-      <c r="EG25" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
+      <c r="EF25" t="inlineStr"/>
+      <c r="EG25" t="inlineStr"/>
       <c r="EH25" t="inlineStr">
         <is>
           <t>5.49</t>
@@ -11924,12 +11924,12 @@
       </c>
       <c r="EI25" t="inlineStr">
         <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EJ25" t="inlineStr">
+        <is>
           <t>9.52</t>
-        </is>
-      </c>
-      <c r="EJ25" t="inlineStr">
-        <is>
-          <t>1.33</t>
         </is>
       </c>
     </row>
@@ -12316,29 +12316,29 @@
       <c r="DV26" t="b">
         <v>1</v>
       </c>
-      <c r="DW26" t="inlineStr"/>
-      <c r="DX26" t="inlineStr"/>
-      <c r="DY26" t="inlineStr"/>
+      <c r="DW26" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="DX26" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="DY26" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
       <c r="DZ26" t="inlineStr"/>
       <c r="EA26" t="inlineStr"/>
       <c r="EB26" t="inlineStr"/>
       <c r="EC26" t="inlineStr"/>
       <c r="ED26" t="inlineStr"/>
-      <c r="EE26" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="EF26" t="inlineStr">
-        <is>
-          <t>2.71</t>
-        </is>
-      </c>
-      <c r="EG26" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
-      </c>
+      <c r="EE26" t="inlineStr"/>
+      <c r="EF26" t="inlineStr"/>
+      <c r="EG26" t="inlineStr"/>
       <c r="EH26" t="inlineStr">
         <is>
           <t>3.64</t>
@@ -12346,12 +12346,12 @@
       </c>
       <c r="EI26" t="inlineStr">
         <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EJ26" t="inlineStr">
+        <is>
           <t>3.13</t>
-        </is>
-      </c>
-      <c r="EJ26" t="inlineStr">
-        <is>
-          <t>2.27</t>
         </is>
       </c>
     </row>
@@ -12738,13 +12738,29 @@
       <c r="DV27" t="b">
         <v>1</v>
       </c>
-      <c r="DW27" t="inlineStr"/>
-      <c r="DX27" t="inlineStr"/>
-      <c r="DY27" t="inlineStr"/>
-      <c r="DZ27" t="inlineStr"/>
+      <c r="DW27" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="DX27" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="DY27" t="inlineStr">
+        <is>
+          <t>3.32</t>
+        </is>
+      </c>
+      <c r="DZ27" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
       <c r="EA27" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="EB27" t="inlineStr">
@@ -12757,26 +12773,10 @@
           <t>3.00</t>
         </is>
       </c>
-      <c r="ED27" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="EE27" t="inlineStr">
-        <is>
-          <t>1.99</t>
-        </is>
-      </c>
-      <c r="EF27" t="inlineStr">
-        <is>
-          <t>3.32</t>
-        </is>
-      </c>
-      <c r="EG27" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
+      <c r="ED27" t="inlineStr"/>
+      <c r="EE27" t="inlineStr"/>
+      <c r="EF27" t="inlineStr"/>
+      <c r="EG27" t="inlineStr"/>
       <c r="EH27" t="inlineStr">
         <is>
           <t>3.42</t>
@@ -12784,12 +12784,12 @@
       </c>
       <c r="EI27" t="inlineStr">
         <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="EJ27" t="inlineStr">
+        <is>
           <t>3.00</t>
-        </is>
-      </c>
-      <c r="EJ27" t="inlineStr">
-        <is>
-          <t>2.45</t>
         </is>
       </c>
     </row>
@@ -13178,35 +13178,35 @@
       </c>
       <c r="DW28" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="DX28" t="inlineStr">
         <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="DY28" t="inlineStr"/>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="DY28" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
       <c r="DZ28" t="inlineStr"/>
       <c r="EA28" t="inlineStr"/>
       <c r="EB28" t="inlineStr"/>
       <c r="EC28" t="inlineStr"/>
-      <c r="ED28" t="inlineStr"/>
+      <c r="ED28" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
       <c r="EE28" t="inlineStr">
         <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="EF28" t="inlineStr">
-        <is>
-          <t>2.49</t>
-        </is>
-      </c>
-      <c r="EG28" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
-      </c>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="EF28" t="inlineStr"/>
+      <c r="EG28" t="inlineStr"/>
       <c r="EH28" t="inlineStr">
         <is>
           <t>3.88</t>
@@ -13214,12 +13214,12 @@
       </c>
       <c r="EI28" t="inlineStr">
         <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="EJ28" t="inlineStr">
+        <is>
           <t>2.94</t>
-        </is>
-      </c>
-      <c r="EJ28" t="inlineStr">
-        <is>
-          <t>2.30</t>
         </is>
       </c>
     </row>
@@ -13606,18 +13606,34 @@
       <c r="DV29" t="b">
         <v>0</v>
       </c>
-      <c r="DW29" t="inlineStr"/>
-      <c r="DX29" t="inlineStr"/>
-      <c r="DY29" t="inlineStr"/>
-      <c r="DZ29" t="inlineStr"/>
+      <c r="DW29" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="DX29" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="DY29" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="DZ29" t="inlineStr">
+        <is>
+          <t>2.86</t>
+        </is>
+      </c>
       <c r="EA29" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="EB29" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="EC29" t="inlineStr">
@@ -13625,26 +13641,10 @@
           <t>3.17</t>
         </is>
       </c>
-      <c r="ED29" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="EE29" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="EF29" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="EG29" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
+      <c r="ED29" t="inlineStr"/>
+      <c r="EE29" t="inlineStr"/>
+      <c r="EF29" t="inlineStr"/>
+      <c r="EG29" t="inlineStr"/>
       <c r="EH29" t="inlineStr">
         <is>
           <t>3.64</t>
@@ -13652,12 +13652,12 @@
       </c>
       <c r="EI29" t="inlineStr">
         <is>
+          <t>3.58</t>
+        </is>
+      </c>
+      <c r="EJ29" t="inlineStr">
+        <is>
           <t>2.08</t>
-        </is>
-      </c>
-      <c r="EJ29" t="inlineStr">
-        <is>
-          <t>3.58</t>
         </is>
       </c>
     </row>
@@ -14044,18 +14044,34 @@
       <c r="DV30" t="b">
         <v>1</v>
       </c>
-      <c r="DW30" t="inlineStr"/>
-      <c r="DX30" t="inlineStr"/>
-      <c r="DY30" t="inlineStr"/>
-      <c r="DZ30" t="inlineStr"/>
+      <c r="DW30" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="DX30" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="DY30" t="inlineStr">
+        <is>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="DZ30" t="inlineStr">
+        <is>
+          <t>2.97</t>
+        </is>
+      </c>
       <c r="EA30" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="EB30" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="EC30" t="inlineStr">
@@ -14063,26 +14079,10 @@
           <t>3.03</t>
         </is>
       </c>
-      <c r="ED30" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="EE30" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="EF30" t="inlineStr">
-        <is>
-          <t>3.04</t>
-        </is>
-      </c>
-      <c r="EG30" t="inlineStr">
-        <is>
-          <t>1.26</t>
-        </is>
-      </c>
+      <c r="ED30" t="inlineStr"/>
+      <c r="EE30" t="inlineStr"/>
+      <c r="EF30" t="inlineStr"/>
+      <c r="EG30" t="inlineStr"/>
       <c r="EH30" t="inlineStr">
         <is>
           <t>3.48</t>
@@ -14090,12 +14090,12 @@
       </c>
       <c r="EI30" t="inlineStr">
         <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EJ30" t="inlineStr">
+        <is>
           <t>3.38</t>
-        </is>
-      </c>
-      <c r="EJ30" t="inlineStr">
-        <is>
-          <t>2.22</t>
         </is>
       </c>
     </row>
@@ -14484,59 +14484,59 @@
       </c>
       <c r="DW31" t="inlineStr">
         <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="DX31" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="DY31" t="inlineStr">
+        <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="DZ31" t="inlineStr">
+        <is>
+          <t>2.87</t>
+        </is>
+      </c>
+      <c r="EA31" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EB31" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EC31" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="ED31" t="inlineStr">
+        <is>
           <t>1.94</t>
         </is>
       </c>
-      <c r="DX31" t="inlineStr">
+      <c r="EE31" t="inlineStr">
         <is>
           <t>1.87</t>
         </is>
       </c>
-      <c r="DY31" t="inlineStr">
+      <c r="EF31" t="inlineStr">
         <is>
           <t>1.53</t>
         </is>
       </c>
-      <c r="DZ31" t="inlineStr">
+      <c r="EG31" t="inlineStr">
         <is>
           <t>2.41</t>
         </is>
       </c>
-      <c r="EA31" t="inlineStr">
-        <is>
-          <t>2.87</t>
-        </is>
-      </c>
-      <c r="EB31" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="EC31" t="inlineStr">
-        <is>
-          <t>3.14</t>
-        </is>
-      </c>
-      <c r="ED31" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="EE31" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="EF31" t="inlineStr">
-        <is>
-          <t>3.18</t>
-        </is>
-      </c>
-      <c r="EG31" t="inlineStr">
-        <is>
-          <t>1.28</t>
-        </is>
-      </c>
       <c r="EH31" t="inlineStr">
         <is>
           <t>3.61</t>
@@ -14544,12 +14544,12 @@
       </c>
       <c r="EI31" t="inlineStr">
         <is>
+          <t>3.02</t>
+        </is>
+      </c>
+      <c r="EJ31" t="inlineStr">
+        <is>
           <t>2.35</t>
-        </is>
-      </c>
-      <c r="EJ31" t="inlineStr">
-        <is>
-          <t>3.02</t>
         </is>
       </c>
     </row>
@@ -14936,18 +14936,34 @@
       <c r="DV32" t="b">
         <v>0</v>
       </c>
-      <c r="DW32" t="inlineStr"/>
-      <c r="DX32" t="inlineStr"/>
-      <c r="DY32" t="inlineStr"/>
-      <c r="DZ32" t="inlineStr"/>
+      <c r="DW32" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="DX32" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="DY32" t="inlineStr">
+        <is>
+          <t>2.98</t>
+        </is>
+      </c>
+      <c r="DZ32" t="inlineStr">
+        <is>
+          <t>2.72</t>
+        </is>
+      </c>
       <c r="EA32" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="EB32" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="EC32" t="inlineStr">
@@ -14955,26 +14971,10 @@
           <t>3.31</t>
         </is>
       </c>
-      <c r="ED32" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
-      <c r="EE32" t="inlineStr">
-        <is>
-          <t>1.79</t>
-        </is>
-      </c>
-      <c r="EF32" t="inlineStr">
-        <is>
-          <t>2.98</t>
-        </is>
-      </c>
-      <c r="EG32" t="inlineStr">
-        <is>
-          <t>1.26</t>
-        </is>
-      </c>
+      <c r="ED32" t="inlineStr"/>
+      <c r="EE32" t="inlineStr"/>
+      <c r="EF32" t="inlineStr"/>
+      <c r="EG32" t="inlineStr"/>
       <c r="EH32" t="inlineStr">
         <is>
           <t>4.27</t>
@@ -14982,12 +14982,12 @@
       </c>
       <c r="EI32" t="inlineStr">
         <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EJ32" t="inlineStr">
+        <is>
           <t>5.63</t>
-        </is>
-      </c>
-      <c r="EJ32" t="inlineStr">
-        <is>
-          <t>1.60</t>
         </is>
       </c>
     </row>
@@ -15374,23 +15374,23 @@
       <c r="DV33" t="b">
         <v>0</v>
       </c>
-      <c r="DW33" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="DX33" t="inlineStr">
-        <is>
-          <t>2.31</t>
-        </is>
-      </c>
+      <c r="DW33" t="inlineStr"/>
+      <c r="DX33" t="inlineStr"/>
       <c r="DY33" t="inlineStr"/>
       <c r="DZ33" t="inlineStr"/>
       <c r="EA33" t="inlineStr"/>
       <c r="EB33" t="inlineStr"/>
       <c r="EC33" t="inlineStr"/>
-      <c r="ED33" t="inlineStr"/>
-      <c r="EE33" t="inlineStr"/>
+      <c r="ED33" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EE33" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
       <c r="EF33" t="inlineStr"/>
       <c r="EG33" t="inlineStr"/>
       <c r="EH33" t="inlineStr">
@@ -15400,12 +15400,12 @@
       </c>
       <c r="EI33" t="inlineStr">
         <is>
+          <t>4.77</t>
+        </is>
+      </c>
+      <c r="EJ33" t="inlineStr">
+        <is>
           <t>1.70</t>
-        </is>
-      </c>
-      <c r="EJ33" t="inlineStr">
-        <is>
-          <t>4.77</t>
         </is>
       </c>
     </row>
@@ -15792,39 +15792,39 @@
       <c r="DV34" t="b">
         <v>0</v>
       </c>
-      <c r="DW34" t="inlineStr">
+      <c r="DW34" t="inlineStr"/>
+      <c r="DX34" t="inlineStr"/>
+      <c r="DY34" t="inlineStr"/>
+      <c r="DZ34" t="inlineStr">
+        <is>
+          <t>2.57</t>
+        </is>
+      </c>
+      <c r="EA34" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EB34" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EC34" t="inlineStr">
+        <is>
+          <t>3.32</t>
+        </is>
+      </c>
+      <c r="ED34" t="inlineStr">
         <is>
           <t>1.74</t>
         </is>
       </c>
-      <c r="DX34" t="inlineStr">
+      <c r="EE34" t="inlineStr">
         <is>
           <t>2.07</t>
         </is>
       </c>
-      <c r="DY34" t="inlineStr"/>
-      <c r="DZ34" t="inlineStr"/>
-      <c r="EA34" t="inlineStr">
-        <is>
-          <t>2.57</t>
-        </is>
-      </c>
-      <c r="EB34" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="EC34" t="inlineStr">
-        <is>
-          <t>3.32</t>
-        </is>
-      </c>
-      <c r="ED34" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="EE34" t="inlineStr"/>
       <c r="EF34" t="inlineStr"/>
       <c r="EG34" t="inlineStr"/>
       <c r="EH34" t="inlineStr">
@@ -15834,12 +15834,12 @@
       </c>
       <c r="EI34" t="inlineStr">
         <is>
+          <t>3.16</t>
+        </is>
+      </c>
+      <c r="EJ34" t="inlineStr">
+        <is>
           <t>2.22</t>
-        </is>
-      </c>
-      <c r="EJ34" t="inlineStr">
-        <is>
-          <t>3.16</t>
         </is>
       </c>
     </row>
@@ -16228,51 +16228,51 @@
       </c>
       <c r="DW35" t="inlineStr">
         <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="DX35" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="DY35" t="inlineStr">
+        <is>
+          <t>2.57</t>
+        </is>
+      </c>
+      <c r="DZ35" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="EA35" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EB35" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EC35" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="ED35" t="inlineStr">
+        <is>
           <t>1.63</t>
         </is>
       </c>
-      <c r="DX35" t="inlineStr">
+      <c r="EE35" t="inlineStr">
         <is>
           <t>2.21</t>
         </is>
       </c>
-      <c r="DY35" t="inlineStr"/>
-      <c r="DZ35" t="inlineStr"/>
-      <c r="EA35" t="inlineStr">
-        <is>
-          <t>2.46</t>
-        </is>
-      </c>
-      <c r="EB35" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="EC35" t="inlineStr">
-        <is>
-          <t>3.34</t>
-        </is>
-      </c>
-      <c r="ED35" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="EE35" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="EF35" t="inlineStr">
-        <is>
-          <t>2.57</t>
-        </is>
-      </c>
-      <c r="EG35" t="inlineStr">
-        <is>
-          <t>1.20</t>
-        </is>
-      </c>
+      <c r="EF35" t="inlineStr"/>
+      <c r="EG35" t="inlineStr"/>
       <c r="EH35" t="inlineStr">
         <is>
           <t>4.02</t>
@@ -16280,12 +16280,12 @@
       </c>
       <c r="EI35" t="inlineStr">
         <is>
+          <t>4.73</t>
+        </is>
+      </c>
+      <c r="EJ35" t="inlineStr">
+        <is>
           <t>1.74</t>
-        </is>
-      </c>
-      <c r="EJ35" t="inlineStr">
-        <is>
-          <t>4.73</t>
         </is>
       </c>
     </row>
@@ -16672,23 +16672,23 @@
       <c r="DV36" t="b">
         <v>0</v>
       </c>
-      <c r="DW36" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
-      <c r="DX36" t="inlineStr">
-        <is>
-          <t>2.21</t>
-        </is>
-      </c>
+      <c r="DW36" t="inlineStr"/>
+      <c r="DX36" t="inlineStr"/>
       <c r="DY36" t="inlineStr"/>
       <c r="DZ36" t="inlineStr"/>
       <c r="EA36" t="inlineStr"/>
       <c r="EB36" t="inlineStr"/>
       <c r="EC36" t="inlineStr"/>
-      <c r="ED36" t="inlineStr"/>
-      <c r="EE36" t="inlineStr"/>
+      <c r="ED36" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="EE36" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
       <c r="EF36" t="inlineStr"/>
       <c r="EG36" t="inlineStr"/>
       <c r="EH36" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="EI36" t="inlineStr">
         <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EJ36" t="inlineStr">
+        <is>
           <t>4.54</t>
-        </is>
-      </c>
-      <c r="EJ36" t="inlineStr">
-        <is>
-          <t>1.78</t>
         </is>
       </c>
     </row>
@@ -17092,51 +17092,51 @@
       </c>
       <c r="DW37" t="inlineStr">
         <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="DX37" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="DY37" t="inlineStr">
+        <is>
+          <t>2.96</t>
+        </is>
+      </c>
+      <c r="DZ37" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="EA37" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EB37" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EC37" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="ED37" t="inlineStr">
+        <is>
           <t>1.71</t>
         </is>
       </c>
-      <c r="DX37" t="inlineStr">
+      <c r="EE37" t="inlineStr">
         <is>
           <t>2.10</t>
         </is>
       </c>
-      <c r="DY37" t="inlineStr"/>
-      <c r="DZ37" t="inlineStr"/>
-      <c r="EA37" t="inlineStr">
-        <is>
-          <t>2.69</t>
-        </is>
-      </c>
-      <c r="EB37" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="EC37" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="ED37" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="EE37" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
-      <c r="EF37" t="inlineStr">
-        <is>
-          <t>2.96</t>
-        </is>
-      </c>
-      <c r="EG37" t="inlineStr">
-        <is>
-          <t>1.26</t>
-        </is>
-      </c>
+      <c r="EF37" t="inlineStr"/>
+      <c r="EG37" t="inlineStr"/>
       <c r="EH37" t="inlineStr">
         <is>
           <t>4.39</t>
@@ -17144,12 +17144,12 @@
       </c>
       <c r="EI37" t="inlineStr">
         <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EJ37" t="inlineStr">
+        <is>
           <t>6.34</t>
-        </is>
-      </c>
-      <c r="EJ37" t="inlineStr">
-        <is>
-          <t>1.53</t>
         </is>
       </c>
     </row>
@@ -17538,51 +17538,51 @@
       </c>
       <c r="DW38" t="inlineStr">
         <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="DX38" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="DY38" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="DZ38" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="EA38" t="inlineStr">
+        <is>
           <t>1.49</t>
         </is>
       </c>
-      <c r="DX38" t="inlineStr">
+      <c r="EB38" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EC38" t="inlineStr">
+        <is>
+          <t>3.33</t>
+        </is>
+      </c>
+      <c r="ED38" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EE38" t="inlineStr">
         <is>
           <t>2.52</t>
         </is>
       </c>
-      <c r="DY38" t="inlineStr"/>
-      <c r="DZ38" t="inlineStr"/>
-      <c r="EA38" t="inlineStr">
-        <is>
-          <t>2.65</t>
-        </is>
-      </c>
-      <c r="EB38" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="EC38" t="inlineStr">
-        <is>
-          <t>3.33</t>
-        </is>
-      </c>
-      <c r="ED38" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="EE38" t="inlineStr">
-        <is>
-          <t>1.79</t>
-        </is>
-      </c>
-      <c r="EF38" t="inlineStr">
-        <is>
-          <t>2.95</t>
-        </is>
-      </c>
-      <c r="EG38" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
+      <c r="EF38" t="inlineStr"/>
+      <c r="EG38" t="inlineStr"/>
       <c r="EH38" t="inlineStr">
         <is>
           <t>3.95</t>
@@ -17590,12 +17590,12 @@
       </c>
       <c r="EI38" t="inlineStr">
         <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EJ38" t="inlineStr">
+        <is>
           <t>3.88</t>
-        </is>
-      </c>
-      <c r="EJ38" t="inlineStr">
-        <is>
-          <t>1.91</t>
         </is>
       </c>
     </row>
@@ -17984,35 +17984,35 @@
       </c>
       <c r="DW39" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="DX39" t="inlineStr">
         <is>
-          <t>2.04</t>
-        </is>
-      </c>
-      <c r="DY39" t="inlineStr"/>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="DY39" t="inlineStr">
+        <is>
+          <t>2.96</t>
+        </is>
+      </c>
       <c r="DZ39" t="inlineStr"/>
       <c r="EA39" t="inlineStr"/>
       <c r="EB39" t="inlineStr"/>
       <c r="EC39" t="inlineStr"/>
-      <c r="ED39" t="inlineStr"/>
+      <c r="ED39" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
       <c r="EE39" t="inlineStr">
         <is>
-          <t>1.81</t>
-        </is>
-      </c>
-      <c r="EF39" t="inlineStr">
-        <is>
-          <t>2.96</t>
-        </is>
-      </c>
-      <c r="EG39" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EF39" t="inlineStr"/>
+      <c r="EG39" t="inlineStr"/>
       <c r="EH39" t="inlineStr">
         <is>
           <t>4.85</t>
@@ -18020,12 +18020,12 @@
       </c>
       <c r="EI39" t="inlineStr">
         <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EJ39" t="inlineStr">
+        <is>
           <t>8.71</t>
-        </is>
-      </c>
-      <c r="EJ39" t="inlineStr">
-        <is>
-          <t>1.39</t>
         </is>
       </c>
     </row>
@@ -18414,35 +18414,35 @@
       </c>
       <c r="DW40" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="DX40" t="inlineStr">
         <is>
-          <t>2.46</t>
-        </is>
-      </c>
-      <c r="DY40" t="inlineStr"/>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="DY40" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
       <c r="DZ40" t="inlineStr"/>
       <c r="EA40" t="inlineStr"/>
       <c r="EB40" t="inlineStr"/>
       <c r="EC40" t="inlineStr"/>
-      <c r="ED40" t="inlineStr"/>
+      <c r="ED40" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
       <c r="EE40" t="inlineStr">
         <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="EF40" t="inlineStr">
-        <is>
-          <t>2.41</t>
-        </is>
-      </c>
-      <c r="EG40" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
-      </c>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="EF40" t="inlineStr"/>
+      <c r="EG40" t="inlineStr"/>
       <c r="EH40" t="inlineStr">
         <is>
           <t>4.31</t>
@@ -18450,12 +18450,12 @@
       </c>
       <c r="EI40" t="inlineStr">
         <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EJ40" t="inlineStr">
+        <is>
           <t>5.26</t>
-        </is>
-      </c>
-      <c r="EJ40" t="inlineStr">
-        <is>
-          <t>1.62</t>
         </is>
       </c>
     </row>
@@ -18844,51 +18844,51 @@
       </c>
       <c r="DW41" t="inlineStr">
         <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="DX41" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="DY41" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="DZ41" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
+      <c r="EA41" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EB41" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EC41" t="inlineStr">
+        <is>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="ED41" t="inlineStr">
+        <is>
           <t>1.60</t>
         </is>
       </c>
-      <c r="DX41" t="inlineStr">
+      <c r="EE41" t="inlineStr">
         <is>
           <t>2.26</t>
         </is>
       </c>
-      <c r="DY41" t="inlineStr"/>
-      <c r="DZ41" t="inlineStr"/>
-      <c r="EA41" t="inlineStr">
-        <is>
-          <t>2.76</t>
-        </is>
-      </c>
-      <c r="EB41" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="EC41" t="inlineStr">
-        <is>
-          <t>3.19</t>
-        </is>
-      </c>
-      <c r="ED41" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="EE41" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="EF41" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="EG41" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
+      <c r="EF41" t="inlineStr"/>
+      <c r="EG41" t="inlineStr"/>
       <c r="EH41" t="inlineStr">
         <is>
           <t>3.63</t>
@@ -18896,12 +18896,12 @@
       </c>
       <c r="EI41" t="inlineStr">
         <is>
+          <t>3.74</t>
+        </is>
+      </c>
+      <c r="EJ41" t="inlineStr">
+        <is>
           <t>2.04</t>
-        </is>
-      </c>
-      <c r="EJ41" t="inlineStr">
-        <is>
-          <t>3.74</t>
         </is>
       </c>
     </row>
@@ -19290,51 +19290,51 @@
       </c>
       <c r="DW42" t="inlineStr">
         <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="DX42" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="DY42" t="inlineStr">
+        <is>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="DZ42" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="EA42" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EB42" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EC42" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="ED42" t="inlineStr">
+        <is>
           <t>1.73</t>
         </is>
       </c>
-      <c r="DX42" t="inlineStr">
+      <c r="EE42" t="inlineStr">
         <is>
           <t>2.07</t>
         </is>
       </c>
-      <c r="DY42" t="inlineStr"/>
-      <c r="DZ42" t="inlineStr"/>
-      <c r="EA42" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="EB42" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="EC42" t="inlineStr">
-        <is>
-          <t>3.15</t>
-        </is>
-      </c>
-      <c r="ED42" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="EE42" t="inlineStr">
-        <is>
-          <t>1.89</t>
-        </is>
-      </c>
-      <c r="EF42" t="inlineStr">
-        <is>
-          <t>3.19</t>
-        </is>
-      </c>
-      <c r="EG42" t="inlineStr">
-        <is>
-          <t>1.28</t>
-        </is>
-      </c>
+      <c r="EF42" t="inlineStr"/>
+      <c r="EG42" t="inlineStr"/>
       <c r="EH42" t="inlineStr">
         <is>
           <t>4.69</t>
@@ -19342,12 +19342,12 @@
       </c>
       <c r="EI42" t="inlineStr">
         <is>
+          <t>7.32</t>
+        </is>
+      </c>
+      <c r="EJ42" t="inlineStr">
+        <is>
           <t>1.45</t>
-        </is>
-      </c>
-      <c r="EJ42" t="inlineStr">
-        <is>
-          <t>7.32</t>
         </is>
       </c>
     </row>
@@ -19734,39 +19734,39 @@
       <c r="DV43" t="b">
         <v>0</v>
       </c>
-      <c r="DW43" t="inlineStr">
+      <c r="DW43" t="inlineStr"/>
+      <c r="DX43" t="inlineStr"/>
+      <c r="DY43" t="inlineStr"/>
+      <c r="DZ43" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="EA43" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EB43" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EC43" t="inlineStr">
+        <is>
+          <t>3.07</t>
+        </is>
+      </c>
+      <c r="ED43" t="inlineStr">
         <is>
           <t>1.65</t>
         </is>
       </c>
-      <c r="DX43" t="inlineStr">
+      <c r="EE43" t="inlineStr">
         <is>
           <t>2.20</t>
         </is>
       </c>
-      <c r="DY43" t="inlineStr"/>
-      <c r="DZ43" t="inlineStr"/>
-      <c r="EA43" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="EB43" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="EC43" t="inlineStr">
-        <is>
-          <t>3.07</t>
-        </is>
-      </c>
-      <c r="ED43" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="EE43" t="inlineStr"/>
       <c r="EF43" t="inlineStr"/>
       <c r="EG43" t="inlineStr"/>
       <c r="EH43" t="inlineStr">
@@ -19776,12 +19776,12 @@
       </c>
       <c r="EI43" t="inlineStr">
         <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="EJ43" t="inlineStr">
+        <is>
           <t>3.08</t>
-        </is>
-      </c>
-      <c r="EJ43" t="inlineStr">
-        <is>
-          <t>2.35</t>
         </is>
       </c>
     </row>
@@ -20168,29 +20168,29 @@
       <c r="DV44" t="b">
         <v>0</v>
       </c>
-      <c r="DW44" t="inlineStr"/>
-      <c r="DX44" t="inlineStr"/>
-      <c r="DY44" t="inlineStr"/>
+      <c r="DW44" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="DX44" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="DY44" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
       <c r="DZ44" t="inlineStr"/>
       <c r="EA44" t="inlineStr"/>
       <c r="EB44" t="inlineStr"/>
       <c r="EC44" t="inlineStr"/>
       <c r="ED44" t="inlineStr"/>
-      <c r="EE44" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="EF44" t="inlineStr">
-        <is>
-          <t>2.76</t>
-        </is>
-      </c>
-      <c r="EG44" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
-      </c>
+      <c r="EE44" t="inlineStr"/>
+      <c r="EF44" t="inlineStr"/>
+      <c r="EG44" t="inlineStr"/>
       <c r="EH44" t="inlineStr">
         <is>
           <t>3.94</t>
@@ -20198,12 +20198,12 @@
       </c>
       <c r="EI44" t="inlineStr">
         <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EJ44" t="inlineStr">
+        <is>
           <t>5.82</t>
-        </is>
-      </c>
-      <c r="EJ44" t="inlineStr">
-        <is>
-          <t>1.64</t>
         </is>
       </c>
     </row>
@@ -20592,51 +20592,51 @@
       </c>
       <c r="DW45" t="inlineStr">
         <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="DX45" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="DY45" t="inlineStr">
+        <is>
+          <t>4.14</t>
+        </is>
+      </c>
+      <c r="DZ45" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="EA45" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EB45" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EC45" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="ED45" t="inlineStr">
+        <is>
           <t>1.62</t>
         </is>
       </c>
-      <c r="DX45" t="inlineStr">
+      <c r="EE45" t="inlineStr">
         <is>
           <t>2.23</t>
         </is>
       </c>
-      <c r="DY45" t="inlineStr"/>
-      <c r="DZ45" t="inlineStr"/>
-      <c r="EA45" t="inlineStr">
-        <is>
-          <t>3.35</t>
-        </is>
-      </c>
-      <c r="EB45" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="EC45" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-      <c r="ED45" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="EE45" t="inlineStr">
-        <is>
-          <t>2.27</t>
-        </is>
-      </c>
-      <c r="EF45" t="inlineStr">
-        <is>
-          <t>4.14</t>
-        </is>
-      </c>
-      <c r="EG45" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
+      <c r="EF45" t="inlineStr"/>
+      <c r="EG45" t="inlineStr"/>
       <c r="EH45" t="inlineStr">
         <is>
           <t>3.21</t>
@@ -20644,12 +20644,12 @@
       </c>
       <c r="EI45" t="inlineStr">
         <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="EJ45" t="inlineStr">
+        <is>
           <t>3.11</t>
-        </is>
-      </c>
-      <c r="EJ45" t="inlineStr">
-        <is>
-          <t>2.50</t>
         </is>
       </c>
     </row>
@@ -21038,35 +21038,35 @@
       </c>
       <c r="DW46" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="DX46" t="inlineStr">
         <is>
-          <t>2.11</t>
-        </is>
-      </c>
-      <c r="DY46" t="inlineStr"/>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="DY46" t="inlineStr">
+        <is>
+          <t>3.21</t>
+        </is>
+      </c>
       <c r="DZ46" t="inlineStr"/>
       <c r="EA46" t="inlineStr"/>
       <c r="EB46" t="inlineStr"/>
       <c r="EC46" t="inlineStr"/>
-      <c r="ED46" t="inlineStr"/>
+      <c r="ED46" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
       <c r="EE46" t="inlineStr">
         <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="EF46" t="inlineStr">
-        <is>
-          <t>3.21</t>
-        </is>
-      </c>
-      <c r="EG46" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="EF46" t="inlineStr"/>
+      <c r="EG46" t="inlineStr"/>
       <c r="EH46" t="inlineStr">
         <is>
           <t>3.59</t>
@@ -21074,12 +21074,12 @@
       </c>
       <c r="EI46" t="inlineStr">
         <is>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="EJ46" t="inlineStr">
+        <is>
           <t>2.27</t>
-        </is>
-      </c>
-      <c r="EJ46" t="inlineStr">
-        <is>
-          <t>3.19</t>
         </is>
       </c>
     </row>
@@ -21468,51 +21468,51 @@
       </c>
       <c r="DW47" t="inlineStr">
         <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="DX47" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="DY47" t="inlineStr">
+        <is>
+          <t>2.61</t>
+        </is>
+      </c>
+      <c r="DZ47" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
+      <c r="EA47" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EB47" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EC47" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="ED47" t="inlineStr">
+        <is>
           <t>1.76</t>
         </is>
       </c>
-      <c r="DX47" t="inlineStr">
+      <c r="EE47" t="inlineStr">
         <is>
           <t>2.03</t>
         </is>
       </c>
-      <c r="DY47" t="inlineStr"/>
-      <c r="DZ47" t="inlineStr"/>
-      <c r="EA47" t="inlineStr">
-        <is>
-          <t>2.44</t>
-        </is>
-      </c>
-      <c r="EB47" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="EC47" t="inlineStr">
-        <is>
-          <t>3.35</t>
-        </is>
-      </c>
-      <c r="ED47" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="EE47" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="EF47" t="inlineStr">
-        <is>
-          <t>2.61</t>
-        </is>
-      </c>
-      <c r="EG47" t="inlineStr">
-        <is>
-          <t>1.20</t>
-        </is>
-      </c>
+      <c r="EF47" t="inlineStr"/>
+      <c r="EG47" t="inlineStr"/>
       <c r="EH47" t="inlineStr">
         <is>
           <t>4.58</t>
@@ -21520,12 +21520,12 @@
       </c>
       <c r="EI47" t="inlineStr">
         <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EJ47" t="inlineStr">
+        <is>
           <t>6.42</t>
-        </is>
-      </c>
-      <c r="EJ47" t="inlineStr">
-        <is>
-          <t>1.51</t>
         </is>
       </c>
     </row>
@@ -21914,35 +21914,35 @@
       </c>
       <c r="DW48" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="DX48" t="inlineStr">
         <is>
-          <t>2.47</t>
-        </is>
-      </c>
-      <c r="DY48" t="inlineStr"/>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="DY48" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
       <c r="DZ48" t="inlineStr"/>
       <c r="EA48" t="inlineStr"/>
       <c r="EB48" t="inlineStr"/>
       <c r="EC48" t="inlineStr"/>
-      <c r="ED48" t="inlineStr"/>
+      <c r="ED48" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
       <c r="EE48" t="inlineStr">
         <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="EF48" t="inlineStr">
-        <is>
-          <t>2.85</t>
-        </is>
-      </c>
-      <c r="EG48" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
+          <t>2.47</t>
+        </is>
+      </c>
+      <c r="EF48" t="inlineStr"/>
+      <c r="EG48" t="inlineStr"/>
       <c r="EH48" t="inlineStr">
         <is>
           <t>3.73</t>
@@ -21950,12 +21950,12 @@
       </c>
       <c r="EI48" t="inlineStr">
         <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="EJ48" t="inlineStr">
+        <is>
           <t>2.01</t>
-        </is>
-      </c>
-      <c r="EJ48" t="inlineStr">
-        <is>
-          <t>3.72</t>
         </is>
       </c>
     </row>
@@ -22342,18 +22342,34 @@
       <c r="DV49" t="b">
         <v>1</v>
       </c>
-      <c r="DW49" t="inlineStr"/>
-      <c r="DX49" t="inlineStr"/>
-      <c r="DY49" t="inlineStr"/>
-      <c r="DZ49" t="inlineStr"/>
+      <c r="DW49" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="DX49" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="DY49" t="inlineStr">
+        <is>
+          <t>3.07</t>
+        </is>
+      </c>
+      <c r="DZ49" t="inlineStr">
+        <is>
+          <t>2.73</t>
+        </is>
+      </c>
       <c r="EA49" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="EB49" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="EC49" t="inlineStr">
@@ -22361,26 +22377,10 @@
           <t>3.25</t>
         </is>
       </c>
-      <c r="ED49" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
-      <c r="EE49" t="inlineStr">
-        <is>
-          <t>1.84</t>
-        </is>
-      </c>
-      <c r="EF49" t="inlineStr">
-        <is>
-          <t>3.07</t>
-        </is>
-      </c>
-      <c r="EG49" t="inlineStr">
-        <is>
-          <t>1.26</t>
-        </is>
-      </c>
+      <c r="ED49" t="inlineStr"/>
+      <c r="EE49" t="inlineStr"/>
+      <c r="EF49" t="inlineStr"/>
+      <c r="EG49" t="inlineStr"/>
       <c r="EH49" t="inlineStr">
         <is>
           <t>4.24</t>
@@ -22388,12 +22388,12 @@
       </c>
       <c r="EI49" t="inlineStr">
         <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EJ49" t="inlineStr">
+        <is>
           <t>6.08</t>
-        </is>
-      </c>
-      <c r="EJ49" t="inlineStr">
-        <is>
-          <t>1.57</t>
         </is>
       </c>
     </row>
@@ -22782,41 +22782,41 @@
       </c>
       <c r="DW50" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="DX50" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="DY50" t="inlineStr">
         <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="DZ50" t="inlineStr">
-        <is>
-          <t>2.57</t>
-        </is>
-      </c>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="DZ50" t="inlineStr"/>
       <c r="EA50" t="inlineStr"/>
       <c r="EB50" t="inlineStr"/>
       <c r="EC50" t="inlineStr"/>
-      <c r="ED50" t="inlineStr"/>
+      <c r="ED50" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
       <c r="EE50" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="EF50" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="EG50" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="EH50" t="inlineStr">
@@ -22826,12 +22826,12 @@
       </c>
       <c r="EI50" t="inlineStr">
         <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EJ50" t="inlineStr">
+        <is>
           <t>6.64</t>
-        </is>
-      </c>
-      <c r="EJ50" t="inlineStr">
-        <is>
-          <t>1.52</t>
         </is>
       </c>
     </row>
@@ -23218,23 +23218,23 @@
       <c r="DV51" t="b">
         <v>0</v>
       </c>
-      <c r="DW51" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="DX51" t="inlineStr">
-        <is>
-          <t>2.22</t>
-        </is>
-      </c>
+      <c r="DW51" t="inlineStr"/>
+      <c r="DX51" t="inlineStr"/>
       <c r="DY51" t="inlineStr"/>
       <c r="DZ51" t="inlineStr"/>
       <c r="EA51" t="inlineStr"/>
       <c r="EB51" t="inlineStr"/>
       <c r="EC51" t="inlineStr"/>
-      <c r="ED51" t="inlineStr"/>
-      <c r="EE51" t="inlineStr"/>
+      <c r="ED51" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EE51" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
       <c r="EF51" t="inlineStr"/>
       <c r="EG51" t="inlineStr"/>
       <c r="EH51" t="inlineStr">
@@ -23244,12 +23244,12 @@
       </c>
       <c r="EI51" t="inlineStr">
         <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EJ51" t="inlineStr">
+        <is>
           <t>3.31</t>
-        </is>
-      </c>
-      <c r="EJ51" t="inlineStr">
-        <is>
-          <t>2.15</t>
         </is>
       </c>
     </row>
@@ -23636,29 +23636,29 @@
       <c r="DV52" t="b">
         <v>0</v>
       </c>
-      <c r="DW52" t="inlineStr"/>
-      <c r="DX52" t="inlineStr"/>
-      <c r="DY52" t="inlineStr"/>
+      <c r="DW52" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="DX52" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="DY52" t="inlineStr">
+        <is>
+          <t>3.47</t>
+        </is>
+      </c>
       <c r="DZ52" t="inlineStr"/>
       <c r="EA52" t="inlineStr"/>
       <c r="EB52" t="inlineStr"/>
       <c r="EC52" t="inlineStr"/>
       <c r="ED52" t="inlineStr"/>
-      <c r="EE52" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="EF52" t="inlineStr">
-        <is>
-          <t>3.47</t>
-        </is>
-      </c>
-      <c r="EG52" t="inlineStr">
-        <is>
-          <t>1.31</t>
-        </is>
-      </c>
+      <c r="EE52" t="inlineStr"/>
+      <c r="EF52" t="inlineStr"/>
+      <c r="EG52" t="inlineStr"/>
       <c r="EH52" t="inlineStr">
         <is>
           <t>3.78</t>
@@ -23666,12 +23666,12 @@
       </c>
       <c r="EI52" t="inlineStr">
         <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EJ52" t="inlineStr">
+        <is>
           <t>4.25</t>
-        </is>
-      </c>
-      <c r="EJ52" t="inlineStr">
-        <is>
-          <t>1.87</t>
         </is>
       </c>
     </row>
@@ -24058,39 +24058,39 @@
       <c r="DV53" t="b">
         <v>0</v>
       </c>
-      <c r="DW53" t="inlineStr">
+      <c r="DW53" t="inlineStr"/>
+      <c r="DX53" t="inlineStr"/>
+      <c r="DY53" t="inlineStr"/>
+      <c r="DZ53" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="EA53" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EB53" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EC53" t="inlineStr">
+        <is>
+          <t>3.32</t>
+        </is>
+      </c>
+      <c r="ED53" t="inlineStr">
         <is>
           <t>1.74</t>
         </is>
       </c>
-      <c r="DX53" t="inlineStr">
+      <c r="EE53" t="inlineStr">
         <is>
           <t>2.06</t>
         </is>
       </c>
-      <c r="DY53" t="inlineStr"/>
-      <c r="DZ53" t="inlineStr"/>
-      <c r="EA53" t="inlineStr">
-        <is>
-          <t>2.53</t>
-        </is>
-      </c>
-      <c r="EB53" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="EC53" t="inlineStr">
-        <is>
-          <t>3.32</t>
-        </is>
-      </c>
-      <c r="ED53" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="EE53" t="inlineStr"/>
       <c r="EF53" t="inlineStr"/>
       <c r="EG53" t="inlineStr"/>
       <c r="EH53" t="inlineStr">
@@ -24100,12 +24100,12 @@
       </c>
       <c r="EI53" t="inlineStr">
         <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="EJ53" t="inlineStr">
+        <is>
           <t>2.77</t>
-        </is>
-      </c>
-      <c r="EJ53" t="inlineStr">
-        <is>
-          <t>2.46</t>
         </is>
       </c>
     </row>
@@ -24494,35 +24494,35 @@
       </c>
       <c r="DW54" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="DX54" t="inlineStr">
         <is>
-          <t>2.57</t>
-        </is>
-      </c>
-      <c r="DY54" t="inlineStr"/>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="DY54" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
       <c r="DZ54" t="inlineStr"/>
       <c r="EA54" t="inlineStr"/>
       <c r="EB54" t="inlineStr"/>
       <c r="EC54" t="inlineStr"/>
-      <c r="ED54" t="inlineStr"/>
+      <c r="ED54" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
       <c r="EE54" t="inlineStr">
         <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="EF54" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
-      <c r="EG54" t="inlineStr">
-        <is>
-          <t>1.13</t>
-        </is>
-      </c>
+          <t>2.57</t>
+        </is>
+      </c>
+      <c r="EF54" t="inlineStr"/>
+      <c r="EG54" t="inlineStr"/>
       <c r="EH54" t="inlineStr">
         <is>
           <t>7.64</t>
@@ -24530,12 +24530,12 @@
       </c>
       <c r="EI54" t="inlineStr">
         <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="EJ54" t="inlineStr">
+        <is>
           <t>12.80</t>
-        </is>
-      </c>
-      <c r="EJ54" t="inlineStr">
-        <is>
-          <t>1.20</t>
         </is>
       </c>
     </row>
@@ -24924,35 +24924,43 @@
       </c>
       <c r="DW55" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="DX55" t="inlineStr">
         <is>
-          <t>2.33</t>
-        </is>
-      </c>
-      <c r="DY55" t="inlineStr"/>
-      <c r="DZ55" t="inlineStr"/>
-      <c r="EA55" t="inlineStr"/>
-      <c r="EB55" t="inlineStr"/>
-      <c r="EC55" t="inlineStr"/>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="DY55" t="inlineStr">
+        <is>
+          <t>2.74</t>
+        </is>
+      </c>
+      <c r="DZ55" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="EA55" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EB55" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EC55" t="inlineStr">
+        <is>
+          <t>3.29</t>
+        </is>
+      </c>
       <c r="ED55" t="inlineStr"/>
-      <c r="EE55" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="EF55" t="inlineStr">
-        <is>
-          <t>2.74</t>
-        </is>
-      </c>
-      <c r="EG55" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
-      </c>
+      <c r="EE55" t="inlineStr"/>
+      <c r="EF55" t="inlineStr"/>
+      <c r="EG55" t="inlineStr"/>
       <c r="EH55" t="inlineStr">
         <is>
           <t>3.62</t>
@@ -24960,12 +24968,12 @@
       </c>
       <c r="EI55" t="inlineStr">
         <is>
+          <t>2.68</t>
+        </is>
+      </c>
+      <c r="EJ55" t="inlineStr">
+        <is>
           <t>2.60</t>
-        </is>
-      </c>
-      <c r="EJ55" t="inlineStr">
-        <is>
-          <t>2.68</t>
         </is>
       </c>
     </row>
@@ -25354,59 +25362,43 @@
       </c>
       <c r="DW56" t="inlineStr">
         <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="DX56" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="DY56" t="inlineStr">
+        <is>
+          <t>3.44</t>
+        </is>
+      </c>
+      <c r="DZ56" t="inlineStr"/>
+      <c r="EA56" t="inlineStr"/>
+      <c r="EB56" t="inlineStr"/>
+      <c r="EC56" t="inlineStr"/>
+      <c r="ED56" t="inlineStr">
+        <is>
           <t>1.88</t>
         </is>
       </c>
-      <c r="DX56" t="inlineStr">
+      <c r="EE56" t="inlineStr">
         <is>
           <t>1.93</t>
         </is>
       </c>
-      <c r="DY56" t="inlineStr">
+      <c r="EF56" t="inlineStr">
         <is>
           <t>1.49</t>
         </is>
       </c>
-      <c r="DZ56" t="inlineStr">
+      <c r="EG56" t="inlineStr">
         <is>
           <t>2.49</t>
         </is>
       </c>
-      <c r="EA56" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="EB56" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="EC56" t="inlineStr">
-        <is>
-          <t>2.92</t>
-        </is>
-      </c>
-      <c r="ED56" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="EE56" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="EF56" t="inlineStr">
-        <is>
-          <t>3.44</t>
-        </is>
-      </c>
-      <c r="EG56" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
       <c r="EH56" t="inlineStr">
         <is>
           <t>3.38</t>
@@ -25414,12 +25406,12 @@
       </c>
       <c r="EI56" t="inlineStr">
         <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="EJ56" t="inlineStr">
+        <is>
           <t>2.90</t>
-        </is>
-      </c>
-      <c r="EJ56" t="inlineStr">
-        <is>
-          <t>2.55</t>
         </is>
       </c>
     </row>
@@ -25806,18 +25798,34 @@
       <c r="DV57" t="b">
         <v>0</v>
       </c>
-      <c r="DW57" t="inlineStr"/>
-      <c r="DX57" t="inlineStr"/>
-      <c r="DY57" t="inlineStr"/>
-      <c r="DZ57" t="inlineStr"/>
+      <c r="DW57" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="DX57" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="DY57" t="inlineStr">
+        <is>
+          <t>3.37</t>
+        </is>
+      </c>
+      <c r="DZ57" t="inlineStr">
+        <is>
+          <t>2.99</t>
+        </is>
+      </c>
       <c r="EA57" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="EB57" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="EC57" t="inlineStr">
@@ -25827,24 +25835,16 @@
       </c>
       <c r="ED57" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="EE57" t="inlineStr">
         <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="EF57" t="inlineStr">
-        <is>
-          <t>3.37</t>
-        </is>
-      </c>
-      <c r="EG57" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="EF57" t="inlineStr"/>
+      <c r="EG57" t="inlineStr"/>
       <c r="EH57" t="inlineStr">
         <is>
           <t>3.44</t>
@@ -25852,12 +25852,12 @@
       </c>
       <c r="EI57" t="inlineStr">
         <is>
+          <t>3.43</t>
+        </is>
+      </c>
+      <c r="EJ57" t="inlineStr">
+        <is>
           <t>2.21</t>
-        </is>
-      </c>
-      <c r="EJ57" t="inlineStr">
-        <is>
-          <t>3.43</t>
         </is>
       </c>
     </row>
@@ -26246,59 +26246,59 @@
       </c>
       <c r="DW58" t="inlineStr">
         <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="DX58" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="DY58" t="inlineStr">
+        <is>
+          <t>3.53</t>
+        </is>
+      </c>
+      <c r="DZ58" t="inlineStr">
+        <is>
+          <t>3.03</t>
+        </is>
+      </c>
+      <c r="EA58" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EB58" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EC58" t="inlineStr">
+        <is>
+          <t>2.92</t>
+        </is>
+      </c>
+      <c r="ED58" t="inlineStr">
+        <is>
           <t>1.81</t>
         </is>
       </c>
-      <c r="DX58" t="inlineStr">
+      <c r="EE58" t="inlineStr">
         <is>
           <t>2.00</t>
         </is>
       </c>
-      <c r="DY58" t="inlineStr">
+      <c r="EF58" t="inlineStr">
         <is>
           <t>1.45</t>
         </is>
       </c>
-      <c r="DZ58" t="inlineStr">
+      <c r="EG58" t="inlineStr">
         <is>
           <t>2.58</t>
         </is>
       </c>
-      <c r="EA58" t="inlineStr">
-        <is>
-          <t>3.03</t>
-        </is>
-      </c>
-      <c r="EB58" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="EC58" t="inlineStr">
-        <is>
-          <t>2.92</t>
-        </is>
-      </c>
-      <c r="ED58" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="EE58" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="EF58" t="inlineStr">
-        <is>
-          <t>3.53</t>
-        </is>
-      </c>
-      <c r="EG58" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
       <c r="EH58" t="inlineStr">
         <is>
           <t>3.45</t>
@@ -26306,12 +26306,12 @@
       </c>
       <c r="EI58" t="inlineStr">
         <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="EJ58" t="inlineStr">
+        <is>
           <t>3.04</t>
-        </is>
-      </c>
-      <c r="EJ58" t="inlineStr">
-        <is>
-          <t>2.41</t>
         </is>
       </c>
     </row>
@@ -26379,13 +26379,13 @@
         <v>3</v>
       </c>
       <c r="S59" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T59" t="n">
         <v>12</v>
       </c>
       <c r="U59" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V59" t="n">
         <v>15</v>
@@ -26397,10 +26397,10 @@
         <v>11</v>
       </c>
       <c r="Y59" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="Z59" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="AA59" t="inlineStr"/>
       <c r="AB59" t="inlineStr"/>
@@ -26552,13 +26552,13 @@
         <v>100</v>
       </c>
       <c r="BZ59" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="CA59" t="n">
         <v>1.46</v>
       </c>
       <c r="CB59" t="n">
-        <v>3.09</v>
+        <v>3.02</v>
       </c>
       <c r="CC59" t="n">
         <v>1</v>
@@ -26615,10 +26615,10 @@
         <v>1</v>
       </c>
       <c r="CU59" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="CV59" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="CW59" t="n">
         <v>1</v>
@@ -26700,41 +26700,41 @@
       </c>
       <c r="DW59" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="DX59" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="DY59" t="inlineStr">
         <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="DZ59" t="inlineStr">
-        <is>
-          <t>2.26</t>
-        </is>
-      </c>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="DZ59" t="inlineStr"/>
       <c r="EA59" t="inlineStr"/>
       <c r="EB59" t="inlineStr"/>
       <c r="EC59" t="inlineStr"/>
-      <c r="ED59" t="inlineStr"/>
+      <c r="ED59" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
       <c r="EE59" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="EF59" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EG59" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="EH59" t="inlineStr">
@@ -26744,12 +26744,12 @@
       </c>
       <c r="EI59" t="inlineStr">
         <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EJ59" t="inlineStr">
+        <is>
           <t>5.27</t>
-        </is>
-      </c>
-      <c r="EJ59" t="inlineStr">
-        <is>
-          <t>1.68</t>
         </is>
       </c>
     </row>
